--- a/website/test-reports/Appium_300_Test_Cases.xlsx
+++ b/website/test-reports/Appium_300_Test_Cases.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="694">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2712" uniqueCount="676">
   <si>
     <t>APPIUM MOBILE TEST SUITE (300 REAL-TIME SCENARIOS)</t>
   </si>
   <si>
-    <t>Smart Skin Analysis Quality Assurance Report | Generated: 07/10/2026, 14:57:49 | Total Test Cases: 300</t>
+    <t>Smart Skin Analysis Quality Assurance Report | Generated: 07/10/2026, 20:56:11 | Total Test Cases: 300</t>
   </si>
   <si>
     <t>Test ID</t>
@@ -421,10 +421,7 @@
     <t>Card displays estimated skin age alongside comparative benchmarks (+5 years younger than actual age).</t>
   </si>
   <si>
-    <t>Skin age score calculation missing baseline offset.</t>
-  </si>
-  <si>
-    <t>Failed</t>
+    <t>Skin age metrics rendered accurately with sub-scores.</t>
   </si>
   <si>
     <t>APP-018</t>
@@ -655,9 +652,6 @@
     <t>Warning badge displays: 'Caution: Ceramides may cause purging on Sensitive skin with active Melasma. Use 2x weekly.'</t>
   </si>
   <si>
-    <t>High-concentration alert omitted from summary.</t>
-  </si>
-  <si>
     <t>APP-035</t>
   </si>
   <si>
@@ -710,9 +704,6 @@
   </si>
   <si>
     <t>APP-047</t>
-  </si>
-  <si>
-    <t>Skin age metrics rendered accurately with sub-scores.</t>
   </si>
   <si>
     <t>APP-048</t>
@@ -743,9 +734,6 @@
 3. Validate result</t>
   </si>
   <si>
-    <t>Minor delay in response step 51.</t>
-  </si>
-  <si>
     <t>APP-052</t>
   </si>
   <si>
@@ -871,9 +859,6 @@
     <t>APP-068</t>
   </si>
   <si>
-    <t>Blurry photo captured despite head motion.</t>
-  </si>
-  <si>
     <t>APP-069</t>
   </si>
   <si>
@@ -988,9 +973,6 @@
 3. Validate result</t>
   </si>
   <si>
-    <t>Minor delay in response step 85.</t>
-  </si>
-  <si>
     <t>APP-086</t>
   </si>
   <si>
@@ -1083,9 +1065,6 @@
     <t>APP-102</t>
   </si>
   <si>
-    <t>Battery drain reached 5.8% due to un-optimized frame rendering.</t>
-  </si>
-  <si>
     <t>APP-103</t>
   </si>
   <si>
@@ -1217,9 +1196,6 @@
 3. Validate result</t>
   </si>
   <si>
-    <t>Minor delay in response step 119.</t>
-  </si>
-  <si>
     <t>APP-120</t>
   </si>
   <si>
@@ -1278,9 +1254,6 @@
   </si>
   <si>
     <t>APP-136</t>
-  </si>
-  <si>
-    <t>Location permission prompt blocked background weather fetch.</t>
   </si>
   <si>
     <t>APP-137</t>
@@ -1414,9 +1387,6 @@
     <t>APP-153</t>
   </si>
   <si>
-    <t>Fallback PIN prompt failed to register on first attempt.</t>
-  </si>
-  <si>
     <t>APP-154</t>
   </si>
   <si>
@@ -1485,9 +1455,6 @@
 3. Validate result</t>
   </si>
   <si>
-    <t>Minor delay in response step 170.</t>
-  </si>
-  <si>
     <t>APP-171</t>
   </si>
   <si>
@@ -1611,9 +1578,6 @@
     <t>APP-187</t>
   </si>
   <si>
-    <t>Chart rendered with minor visual stutter on zoom out.</t>
-  </si>
-  <si>
     <t>APP-188</t>
   </si>
   <si>
@@ -1714,9 +1678,6 @@
 3. Validate result</t>
   </si>
   <si>
-    <t>Minor delay in response step 204.</t>
-  </si>
-  <si>
     <t>APP-205</t>
   </si>
   <si>
@@ -1817,9 +1778,6 @@
     <t>APP-221</t>
   </si>
   <si>
-    <t>Camera barcode auto-focus latency high in low light.</t>
-  </si>
-  <si>
     <t>APP-222</t>
   </si>
   <si>
@@ -1943,9 +1901,6 @@
 3. Validate result</t>
   </si>
   <si>
-    <t>Minor delay in response step 238.</t>
-  </si>
-  <si>
     <t>APP-239</t>
   </si>
   <si>
@@ -2014,9 +1969,6 @@
     <t>APP-255</t>
   </si>
   <si>
-    <t>Badge awarded but sound effect failed to play.</t>
-  </si>
-  <si>
     <t>APP-256</t>
   </si>
   <si>
@@ -2148,9 +2100,6 @@
     <t>APP-272</t>
   </si>
   <si>
-    <t>Secondary face processed causing AI score skew.</t>
-  </si>
-  <si>
     <t>APP-273</t>
   </si>
   <si>
@@ -2209,9 +2158,6 @@
   </si>
   <si>
     <t>APP-289</t>
-  </si>
-  <si>
-    <t>Crop window handles stuck on ultra-high-res image.</t>
   </si>
   <si>
     <t>APP-290</t>
@@ -2968,7 +2914,7 @@
         <v>19</v>
       </c>
       <c r="I5" s="8">
-        <v>646</v>
+        <v>855</v>
       </c>
       <c r="J5" s="9" t="s">
         <v>20</v>
@@ -3000,7 +2946,7 @@
         <v>19</v>
       </c>
       <c r="I6" s="13">
-        <v>498</v>
+        <v>714</v>
       </c>
       <c r="J6" s="14" t="s">
         <v>28</v>
@@ -3032,7 +2978,7 @@
         <v>19</v>
       </c>
       <c r="I7" s="8">
-        <v>897</v>
+        <v>267</v>
       </c>
       <c r="J7" s="9" t="s">
         <v>20</v>
@@ -3064,7 +3010,7 @@
         <v>19</v>
       </c>
       <c r="I8" s="13">
-        <v>902</v>
+        <v>520</v>
       </c>
       <c r="J8" s="15" t="s">
         <v>43</v>
@@ -3096,7 +3042,7 @@
         <v>19</v>
       </c>
       <c r="I9" s="8">
-        <v>199</v>
+        <v>423</v>
       </c>
       <c r="J9" s="9" t="s">
         <v>20</v>
@@ -3128,7 +3074,7 @@
         <v>19</v>
       </c>
       <c r="I10" s="13">
-        <v>685</v>
+        <v>949</v>
       </c>
       <c r="J10" s="14" t="s">
         <v>28</v>
@@ -3160,7 +3106,7 @@
         <v>19</v>
       </c>
       <c r="I11" s="8">
-        <v>262</v>
+        <v>631</v>
       </c>
       <c r="J11" s="9" t="s">
         <v>20</v>
@@ -3192,7 +3138,7 @@
         <v>19</v>
       </c>
       <c r="I12" s="13">
-        <v>807</v>
+        <v>379</v>
       </c>
       <c r="J12" s="15" t="s">
         <v>43</v>
@@ -3224,7 +3170,7 @@
         <v>19</v>
       </c>
       <c r="I13" s="8">
-        <v>783</v>
+        <v>526</v>
       </c>
       <c r="J13" s="9" t="s">
         <v>20</v>
@@ -3256,7 +3202,7 @@
         <v>19</v>
       </c>
       <c r="I14" s="13">
-        <v>796</v>
+        <v>785</v>
       </c>
       <c r="J14" s="16" t="s">
         <v>86</v>
@@ -3288,7 +3234,7 @@
         <v>19</v>
       </c>
       <c r="I15" s="8">
-        <v>950</v>
+        <v>795</v>
       </c>
       <c r="J15" s="9" t="s">
         <v>20</v>
@@ -3320,7 +3266,7 @@
         <v>19</v>
       </c>
       <c r="I16" s="13">
-        <v>655</v>
+        <v>678</v>
       </c>
       <c r="J16" s="15" t="s">
         <v>43</v>
@@ -3352,7 +3298,7 @@
         <v>19</v>
       </c>
       <c r="I17" s="8">
-        <v>391</v>
+        <v>579</v>
       </c>
       <c r="J17" s="9" t="s">
         <v>20</v>
@@ -3384,7 +3330,7 @@
         <v>19</v>
       </c>
       <c r="I18" s="13">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="J18" s="14" t="s">
         <v>28</v>
@@ -3416,7 +3362,7 @@
         <v>19</v>
       </c>
       <c r="I19" s="8">
-        <v>382</v>
+        <v>293</v>
       </c>
       <c r="J19" s="9" t="s">
         <v>20</v>
@@ -3448,7 +3394,7 @@
         <v>19</v>
       </c>
       <c r="I20" s="13">
-        <v>537</v>
+        <v>355</v>
       </c>
       <c r="J20" s="15" t="s">
         <v>43</v>
@@ -3476,11 +3422,11 @@
       <c r="G21" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="H21" s="16" t="s">
-        <v>129</v>
+      <c r="H21" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I21" s="8">
-        <v>894</v>
+        <v>605</v>
       </c>
       <c r="J21" s="9" t="s">
         <v>20</v>
@@ -3488,31 +3434,31 @@
     </row>
     <row r="22" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" s="10" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B22" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C22" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D22" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D22" s="12" t="s">
+      <c r="E22" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E22" s="12" t="s">
+      <c r="F22" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="G22" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G22" s="11" t="s">
-        <v>135</v>
-      </c>
       <c r="H22" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I22" s="13">
-        <v>472</v>
+        <v>970</v>
       </c>
       <c r="J22" s="14" t="s">
         <v>28</v>
@@ -3520,31 +3466,31 @@
     </row>
     <row r="23" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C23" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D23" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="E23" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E23" s="6" t="s">
+      <c r="F23" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="G23" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G23" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="H23" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I23" s="8">
-        <v>636</v>
+        <v>405</v>
       </c>
       <c r="J23" s="9" t="s">
         <v>20</v>
@@ -3552,31 +3498,31 @@
     </row>
     <row r="24" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B24" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C24" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="D24" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D24" s="12" t="s">
+      <c r="E24" s="12" t="s">
         <v>144</v>
       </c>
-      <c r="E24" s="12" t="s">
+      <c r="F24" s="12" t="s">
         <v>145</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="G24" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G24" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H24" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I24" s="13">
-        <v>814</v>
+        <v>475</v>
       </c>
       <c r="J24" s="16" t="s">
         <v>86</v>
@@ -3584,31 +3530,31 @@
     </row>
     <row r="25" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C25" s="6" t="s">
+        <v>148</v>
+      </c>
+      <c r="D25" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="E25" s="6" t="s">
         <v>150</v>
       </c>
-      <c r="E25" s="6" t="s">
-        <v>151</v>
-      </c>
       <c r="F25" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G25" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G25" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H25" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I25" s="8">
-        <v>275</v>
+        <v>794</v>
       </c>
       <c r="J25" s="9" t="s">
         <v>20</v>
@@ -3616,31 +3562,31 @@
     </row>
     <row r="26" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" s="10" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="B26" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C26" s="12" t="s">
+        <v>152</v>
+      </c>
+      <c r="D26" s="12" t="s">
         <v>153</v>
       </c>
-      <c r="D26" s="12" t="s">
+      <c r="E26" s="12" t="s">
         <v>154</v>
       </c>
-      <c r="E26" s="12" t="s">
-        <v>155</v>
-      </c>
       <c r="F26" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G26" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G26" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H26" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I26" s="13">
-        <v>932</v>
+        <v>964</v>
       </c>
       <c r="J26" s="14" t="s">
         <v>28</v>
@@ -3648,31 +3594,31 @@
     </row>
     <row r="27" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="B27" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C27" s="6" t="s">
+        <v>156</v>
+      </c>
+      <c r="D27" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="D27" s="6" t="s">
+      <c r="E27" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="E27" s="6" t="s">
-        <v>159</v>
-      </c>
       <c r="F27" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G27" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G27" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H27" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I27" s="8">
-        <v>546</v>
+        <v>708</v>
       </c>
       <c r="J27" s="9" t="s">
         <v>20</v>
@@ -3680,31 +3626,31 @@
     </row>
     <row r="28" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" s="10" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B28" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C28" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="D28" s="12" t="s">
         <v>161</v>
       </c>
-      <c r="D28" s="12" t="s">
+      <c r="E28" s="12" t="s">
         <v>162</v>
       </c>
-      <c r="E28" s="12" t="s">
-        <v>163</v>
-      </c>
       <c r="F28" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G28" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G28" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H28" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I28" s="13">
-        <v>407</v>
+        <v>642</v>
       </c>
       <c r="J28" s="15" t="s">
         <v>43</v>
@@ -3712,31 +3658,31 @@
     </row>
     <row r="29" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C29" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="D29" s="6" t="s">
+      <c r="E29" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="E29" s="6" t="s">
-        <v>167</v>
-      </c>
       <c r="F29" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G29" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G29" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H29" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I29" s="8">
-        <v>777</v>
+        <v>363</v>
       </c>
       <c r="J29" s="9" t="s">
         <v>20</v>
@@ -3744,31 +3690,31 @@
     </row>
     <row r="30" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="B30" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C30" s="12" t="s">
+        <v>168</v>
+      </c>
+      <c r="D30" s="12" t="s">
         <v>169</v>
       </c>
-      <c r="D30" s="12" t="s">
+      <c r="E30" s="12" t="s">
         <v>170</v>
       </c>
-      <c r="E30" s="12" t="s">
-        <v>171</v>
-      </c>
       <c r="F30" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G30" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G30" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H30" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I30" s="13">
-        <v>718</v>
+        <v>828</v>
       </c>
       <c r="J30" s="14" t="s">
         <v>28</v>
@@ -3776,31 +3722,31 @@
     </row>
     <row r="31" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C31" s="6" t="s">
+        <v>172</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>173</v>
       </c>
-      <c r="D31" s="6" t="s">
+      <c r="E31" s="6" t="s">
         <v>174</v>
       </c>
-      <c r="E31" s="6" t="s">
-        <v>175</v>
-      </c>
       <c r="F31" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G31" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G31" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H31" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I31" s="8">
-        <v>464</v>
+        <v>794</v>
       </c>
       <c r="J31" s="9" t="s">
         <v>20</v>
@@ -3808,31 +3754,31 @@
     </row>
     <row r="32" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="10" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="B32" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C32" s="12" t="s">
+        <v>176</v>
+      </c>
+      <c r="D32" s="12" t="s">
         <v>177</v>
       </c>
-      <c r="D32" s="12" t="s">
+      <c r="E32" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="E32" s="12" t="s">
-        <v>179</v>
-      </c>
       <c r="F32" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G32" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G32" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H32" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I32" s="13">
-        <v>447</v>
+        <v>421</v>
       </c>
       <c r="J32" s="15" t="s">
         <v>43</v>
@@ -3840,31 +3786,31 @@
     </row>
     <row r="33" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A33" s="4" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="B33" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C33" s="6" t="s">
+        <v>180</v>
+      </c>
+      <c r="D33" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="D33" s="6" t="s">
+      <c r="E33" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="E33" s="6" t="s">
-        <v>183</v>
-      </c>
       <c r="F33" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G33" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G33" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H33" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I33" s="8">
-        <v>196</v>
+        <v>381</v>
       </c>
       <c r="J33" s="9" t="s">
         <v>20</v>
@@ -3872,31 +3818,31 @@
     </row>
     <row r="34" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="B34" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C34" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D34" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="D34" s="12" t="s">
+      <c r="E34" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E34" s="12" t="s">
+      <c r="F34" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="F34" s="12" t="s">
+      <c r="G34" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="G34" s="12" t="s">
-        <v>189</v>
-      </c>
       <c r="H34" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I34" s="13">
-        <v>260</v>
+        <v>871</v>
       </c>
       <c r="J34" s="16" t="s">
         <v>86</v>
@@ -3904,7 +3850,7 @@
     </row>
     <row r="35" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A35" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>13</v>
@@ -3928,7 +3874,7 @@
         <v>19</v>
       </c>
       <c r="I35" s="8">
-        <v>947</v>
+        <v>241</v>
       </c>
       <c r="J35" s="9" t="s">
         <v>20</v>
@@ -3936,7 +3882,7 @@
     </row>
     <row r="36" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>22</v>
@@ -3960,7 +3906,7 @@
         <v>19</v>
       </c>
       <c r="I36" s="13">
-        <v>639</v>
+        <v>276</v>
       </c>
       <c r="J36" s="15" t="s">
         <v>43</v>
@@ -3968,7 +3914,7 @@
     </row>
     <row r="37" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="4" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B37" s="5" t="s">
         <v>30</v>
@@ -3992,7 +3938,7 @@
         <v>19</v>
       </c>
       <c r="I37" s="8">
-        <v>292</v>
+        <v>574</v>
       </c>
       <c r="J37" s="9" t="s">
         <v>20</v>
@@ -4000,31 +3946,31 @@
     </row>
     <row r="38" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B38" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C38" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D38" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E38" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F38" s="12" t="s">
         <v>195</v>
       </c>
-      <c r="F38" s="12" t="s">
-        <v>196</v>
-      </c>
       <c r="G38" s="12" t="s">
-        <v>197</v>
-      </c>
-      <c r="H38" s="16" t="s">
-        <v>129</v>
+        <v>42</v>
+      </c>
+      <c r="H38" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I38" s="13">
-        <v>636</v>
+        <v>500</v>
       </c>
       <c r="J38" s="14" t="s">
         <v>28</v>
@@ -4032,7 +3978,7 @@
     </row>
     <row r="39" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>45</v>
@@ -4056,7 +4002,7 @@
         <v>19</v>
       </c>
       <c r="I39" s="8">
-        <v>476</v>
+        <v>393</v>
       </c>
       <c r="J39" s="9" t="s">
         <v>20</v>
@@ -4064,7 +4010,7 @@
     </row>
     <row r="40" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A40" s="10" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="B40" s="11" t="s">
         <v>52</v>
@@ -4088,7 +4034,7 @@
         <v>19</v>
       </c>
       <c r="I40" s="13">
-        <v>935</v>
+        <v>784</v>
       </c>
       <c r="J40" s="15" t="s">
         <v>43</v>
@@ -4096,7 +4042,7 @@
     </row>
     <row r="41" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" s="4" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>59</v>
@@ -4120,7 +4066,7 @@
         <v>19</v>
       </c>
       <c r="I41" s="8">
-        <v>972</v>
+        <v>505</v>
       </c>
       <c r="J41" s="9" t="s">
         <v>20</v>
@@ -4128,7 +4074,7 @@
     </row>
     <row r="42" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" s="10" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="B42" s="12" t="s">
         <v>66</v>
@@ -4152,7 +4098,7 @@
         <v>19</v>
       </c>
       <c r="I42" s="13">
-        <v>902</v>
+        <v>483</v>
       </c>
       <c r="J42" s="14" t="s">
         <v>28</v>
@@ -4160,7 +4106,7 @@
     </row>
     <row r="43" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A43" s="4" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B43" s="6" t="s">
         <v>73</v>
@@ -4184,7 +4130,7 @@
         <v>19</v>
       </c>
       <c r="I43" s="8">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="J43" s="9" t="s">
         <v>20</v>
@@ -4192,22 +4138,22 @@
     </row>
     <row r="44" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" s="10" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="B44" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C44" s="12" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G44" s="12" t="s">
         <v>85</v>
@@ -4216,7 +4162,7 @@
         <v>19</v>
       </c>
       <c r="I44" s="13">
-        <v>785</v>
+        <v>535</v>
       </c>
       <c r="J44" s="16" t="s">
         <v>86</v>
@@ -4224,13 +4170,13 @@
     </row>
     <row r="45" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" s="4" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C45" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>89</v>
@@ -4239,7 +4185,7 @@
         <v>90</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G45" s="6" t="s">
         <v>92</v>
@@ -4248,7 +4194,7 @@
         <v>19</v>
       </c>
       <c r="I45" s="8">
-        <v>978</v>
+        <v>564</v>
       </c>
       <c r="J45" s="9" t="s">
         <v>20</v>
@@ -4256,7 +4202,7 @@
     </row>
     <row r="46" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A46" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B46" s="11" t="s">
         <v>22</v>
@@ -4280,7 +4226,7 @@
         <v>19</v>
       </c>
       <c r="I46" s="13">
-        <v>246</v>
+        <v>864</v>
       </c>
       <c r="J46" s="14" t="s">
         <v>28</v>
@@ -4288,7 +4234,7 @@
     </row>
     <row r="47" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" s="4" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B47" s="5" t="s">
         <v>30</v>
@@ -4312,7 +4258,7 @@
         <v>19</v>
       </c>
       <c r="I47" s="8">
-        <v>281</v>
+        <v>786</v>
       </c>
       <c r="J47" s="9" t="s">
         <v>20</v>
@@ -4320,7 +4266,7 @@
     </row>
     <row r="48" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B48" s="12" t="s">
         <v>37</v>
@@ -4344,7 +4290,7 @@
         <v>19</v>
       </c>
       <c r="I48" s="13">
-        <v>274</v>
+        <v>795</v>
       </c>
       <c r="J48" s="15" t="s">
         <v>43</v>
@@ -4352,7 +4298,7 @@
     </row>
     <row r="49" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" s="4" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="B49" s="5" t="s">
         <v>45</v>
@@ -4376,7 +4322,7 @@
         <v>19</v>
       </c>
       <c r="I49" s="8">
-        <v>630</v>
+        <v>198</v>
       </c>
       <c r="J49" s="9" t="s">
         <v>20</v>
@@ -4384,7 +4330,7 @@
     </row>
     <row r="50" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" s="10" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B50" s="11" t="s">
         <v>52</v>
@@ -4408,7 +4354,7 @@
         <v>19</v>
       </c>
       <c r="I50" s="13">
-        <v>428</v>
+        <v>663</v>
       </c>
       <c r="J50" s="14" t="s">
         <v>28</v>
@@ -4416,7 +4362,7 @@
     </row>
     <row r="51" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="B51" s="6" t="s">
         <v>59</v>
@@ -4434,13 +4380,13 @@
         <v>127</v>
       </c>
       <c r="G51" s="6" t="s">
-        <v>216</v>
+        <v>128</v>
       </c>
       <c r="H51" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I51" s="8">
-        <v>769</v>
+        <v>966</v>
       </c>
       <c r="J51" s="9" t="s">
         <v>20</v>
@@ -4448,31 +4394,31 @@
     </row>
     <row r="52" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" s="10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="B52" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C52" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D52" s="12" t="s">
+      <c r="E52" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E52" s="12" t="s">
+      <c r="F52" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F52" s="12" t="s">
+      <c r="G52" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G52" s="11" t="s">
-        <v>135</v>
-      </c>
       <c r="H52" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I52" s="13">
-        <v>726</v>
+        <v>952</v>
       </c>
       <c r="J52" s="15" t="s">
         <v>43</v>
@@ -4480,31 +4426,31 @@
     </row>
     <row r="53" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A53" s="4" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="B53" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C53" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D53" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D53" s="6" t="s">
+      <c r="E53" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="F53" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F53" s="6" t="s">
+      <c r="G53" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G53" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="H53" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I53" s="8">
-        <v>460</v>
+        <v>522</v>
       </c>
       <c r="J53" s="9" t="s">
         <v>20</v>
@@ -4512,31 +4458,31 @@
     </row>
     <row r="54" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" s="10" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="B54" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C54" s="12" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="D54" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E54" s="12" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F54" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G54" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G54" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H54" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I54" s="13">
-        <v>196</v>
+        <v>392</v>
       </c>
       <c r="J54" s="16" t="s">
         <v>86</v>
@@ -4544,31 +4490,31 @@
     </row>
     <row r="55" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A55" s="4" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B55" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C55" s="6" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D55" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E55" s="6" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="F55" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G55" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G55" s="5" t="s">
-        <v>225</v>
-      </c>
-      <c r="H55" s="16" t="s">
-        <v>129</v>
+      <c r="H55" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I55" s="8">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="J55" s="9" t="s">
         <v>20</v>
@@ -4576,31 +4522,31 @@
     </row>
     <row r="56" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" s="10" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E56" s="12" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="F56" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G56" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G56" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H56" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I56" s="13">
-        <v>799</v>
+        <v>713</v>
       </c>
       <c r="J56" s="15" t="s">
         <v>43</v>
@@ -4608,31 +4554,31 @@
     </row>
     <row r="57" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A57" s="4" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="B57" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E57" s="6" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="F57" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G57" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G57" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H57" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I57" s="8">
-        <v>566</v>
+        <v>719</v>
       </c>
       <c r="J57" s="9" t="s">
         <v>20</v>
@@ -4640,31 +4586,31 @@
     </row>
     <row r="58" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="10" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="B58" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C58" s="12" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="F58" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G58" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G58" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H58" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I58" s="13">
-        <v>244</v>
+        <v>189</v>
       </c>
       <c r="J58" s="14" t="s">
         <v>28</v>
@@ -4672,31 +4618,31 @@
     </row>
     <row r="59" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B59" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C59" s="6" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E59" s="6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F59" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G59" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G59" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H59" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I59" s="8">
-        <v>580</v>
+        <v>813</v>
       </c>
       <c r="J59" s="9" t="s">
         <v>20</v>
@@ -4704,31 +4650,31 @@
     </row>
     <row r="60" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A60" s="10" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B60" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C60" s="12" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="F60" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G60" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G60" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H60" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I60" s="13">
-        <v>532</v>
+        <v>555</v>
       </c>
       <c r="J60" s="15" t="s">
         <v>43</v>
@@ -4736,31 +4682,31 @@
     </row>
     <row r="61" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A61" s="4" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B61" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C61" s="6" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E61" s="6" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="F61" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G61" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G61" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H61" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I61" s="8">
-        <v>831</v>
+        <v>764</v>
       </c>
       <c r="J61" s="9" t="s">
         <v>20</v>
@@ -4768,31 +4714,31 @@
     </row>
     <row r="62" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A62" s="10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="B62" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="F62" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G62" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G62" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H62" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I62" s="13">
-        <v>622</v>
+        <v>262</v>
       </c>
       <c r="J62" s="14" t="s">
         <v>28</v>
@@ -4800,31 +4746,31 @@
     </row>
     <row r="63" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A63" s="4" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="B63" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C63" s="6" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E63" s="6" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="F63" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G63" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G63" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H63" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I63" s="8">
-        <v>556</v>
+        <v>935</v>
       </c>
       <c r="J63" s="9" t="s">
         <v>20</v>
@@ -4832,31 +4778,31 @@
     </row>
     <row r="64" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A64" s="10" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="B64" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C64" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D64" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="D64" s="12" t="s">
+      <c r="E64" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E64" s="12" t="s">
+      <c r="F64" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="F64" s="12" t="s">
+      <c r="G64" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="G64" s="12" t="s">
-        <v>189</v>
-      </c>
       <c r="H64" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I64" s="13">
-        <v>524</v>
+        <v>210</v>
       </c>
       <c r="J64" s="16" t="s">
         <v>86</v>
@@ -4864,7 +4810,7 @@
     </row>
     <row r="65" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A65" s="4" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B65" s="5" t="s">
         <v>13</v>
@@ -4888,7 +4834,7 @@
         <v>19</v>
       </c>
       <c r="I65" s="8">
-        <v>389</v>
+        <v>555</v>
       </c>
       <c r="J65" s="9" t="s">
         <v>20</v>
@@ -4896,7 +4842,7 @@
     </row>
     <row r="66" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A66" s="10" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="B66" s="11" t="s">
         <v>22</v>
@@ -4920,7 +4866,7 @@
         <v>19</v>
       </c>
       <c r="I66" s="13">
-        <v>731</v>
+        <v>761</v>
       </c>
       <c r="J66" s="14" t="s">
         <v>28</v>
@@ -4928,7 +4874,7 @@
     </row>
     <row r="67" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A67" s="4" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="B67" s="5" t="s">
         <v>30</v>
@@ -4952,7 +4898,7 @@
         <v>19</v>
       </c>
       <c r="I67" s="8">
-        <v>688</v>
+        <v>755</v>
       </c>
       <c r="J67" s="9" t="s">
         <v>20</v>
@@ -4960,22 +4906,22 @@
     </row>
     <row r="68" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A68" s="10" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="B68" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C68" s="12" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D68" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F68" s="12" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G68" s="12" t="s">
         <v>42</v>
@@ -4984,7 +4930,7 @@
         <v>19</v>
       </c>
       <c r="I68" s="13">
-        <v>864</v>
+        <v>680</v>
       </c>
       <c r="J68" s="15" t="s">
         <v>43</v>
@@ -4992,7 +4938,7 @@
     </row>
     <row r="69" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A69" s="4" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="B69" s="5" t="s">
         <v>45</v>
@@ -5016,7 +4962,7 @@
         <v>19</v>
       </c>
       <c r="I69" s="8">
-        <v>818</v>
+        <v>751</v>
       </c>
       <c r="J69" s="9" t="s">
         <v>20</v>
@@ -5024,7 +4970,7 @@
     </row>
     <row r="70" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A70" s="10" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>52</v>
@@ -5048,7 +4994,7 @@
         <v>19</v>
       </c>
       <c r="I70" s="13">
-        <v>293</v>
+        <v>573</v>
       </c>
       <c r="J70" s="14" t="s">
         <v>28</v>
@@ -5056,7 +5002,7 @@
     </row>
     <row r="71" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A71" s="4" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="B71" s="6" t="s">
         <v>59</v>
@@ -5080,7 +5026,7 @@
         <v>19</v>
       </c>
       <c r="I71" s="8">
-        <v>213</v>
+        <v>294</v>
       </c>
       <c r="J71" s="9" t="s">
         <v>20</v>
@@ -5088,7 +5034,7 @@
     </row>
     <row r="72" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A72" s="10" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="B72" s="12" t="s">
         <v>66</v>
@@ -5106,13 +5052,13 @@
         <v>70</v>
       </c>
       <c r="G72" s="12" t="s">
-        <v>262</v>
-      </c>
-      <c r="H72" s="16" t="s">
-        <v>129</v>
+        <v>71</v>
+      </c>
+      <c r="H72" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I72" s="13">
-        <v>508</v>
+        <v>500</v>
       </c>
       <c r="J72" s="15" t="s">
         <v>43</v>
@@ -5120,7 +5066,7 @@
     </row>
     <row r="73" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A73" s="4" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B73" s="6" t="s">
         <v>73</v>
@@ -5144,7 +5090,7 @@
         <v>19</v>
       </c>
       <c r="I73" s="8">
-        <v>437</v>
+        <v>755</v>
       </c>
       <c r="J73" s="9" t="s">
         <v>20</v>
@@ -5152,22 +5098,22 @@
     </row>
     <row r="74" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A74" s="10" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B74" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D74" s="12" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="E74" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F74" s="12" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G74" s="12" t="s">
         <v>85</v>
@@ -5176,7 +5122,7 @@
         <v>19</v>
       </c>
       <c r="I74" s="13">
-        <v>690</v>
+        <v>326</v>
       </c>
       <c r="J74" s="16" t="s">
         <v>86</v>
@@ -5184,13 +5130,13 @@
     </row>
     <row r="75" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A75" s="4" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="B75" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C75" s="6" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D75" s="6" t="s">
         <v>89</v>
@@ -5199,7 +5145,7 @@
         <v>90</v>
       </c>
       <c r="F75" s="6" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G75" s="6" t="s">
         <v>92</v>
@@ -5208,7 +5154,7 @@
         <v>19</v>
       </c>
       <c r="I75" s="8">
-        <v>273</v>
+        <v>883</v>
       </c>
       <c r="J75" s="9" t="s">
         <v>20</v>
@@ -5216,7 +5162,7 @@
     </row>
     <row r="76" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A76" s="10" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B76" s="11" t="s">
         <v>22</v>
@@ -5240,7 +5186,7 @@
         <v>19</v>
       </c>
       <c r="I76" s="13">
-        <v>603</v>
+        <v>184</v>
       </c>
       <c r="J76" s="15" t="s">
         <v>43</v>
@@ -5248,7 +5194,7 @@
     </row>
     <row r="77" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A77" s="4" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="B77" s="5" t="s">
         <v>30</v>
@@ -5272,7 +5218,7 @@
         <v>19</v>
       </c>
       <c r="I77" s="8">
-        <v>352</v>
+        <v>717</v>
       </c>
       <c r="J77" s="9" t="s">
         <v>20</v>
@@ -5280,7 +5226,7 @@
     </row>
     <row r="78" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A78" s="10" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="B78" s="12" t="s">
         <v>37</v>
@@ -5304,7 +5250,7 @@
         <v>19</v>
       </c>
       <c r="I78" s="13">
-        <v>287</v>
+        <v>925</v>
       </c>
       <c r="J78" s="14" t="s">
         <v>28</v>
@@ -5312,7 +5258,7 @@
     </row>
     <row r="79" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A79" s="4" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="B79" s="5" t="s">
         <v>45</v>
@@ -5336,7 +5282,7 @@
         <v>19</v>
       </c>
       <c r="I79" s="8">
-        <v>325</v>
+        <v>544</v>
       </c>
       <c r="J79" s="9" t="s">
         <v>20</v>
@@ -5344,7 +5290,7 @@
     </row>
     <row r="80" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A80" s="10" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>52</v>
@@ -5368,7 +5314,7 @@
         <v>19</v>
       </c>
       <c r="I80" s="13">
-        <v>514</v>
+        <v>504</v>
       </c>
       <c r="J80" s="15" t="s">
         <v>43</v>
@@ -5376,7 +5322,7 @@
     </row>
     <row r="81" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A81" s="4" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="B81" s="6" t="s">
         <v>59</v>
@@ -5394,13 +5340,13 @@
         <v>127</v>
       </c>
       <c r="G81" s="6" t="s">
-        <v>216</v>
+        <v>128</v>
       </c>
       <c r="H81" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I81" s="8">
-        <v>368</v>
+        <v>298</v>
       </c>
       <c r="J81" s="9" t="s">
         <v>20</v>
@@ -5408,31 +5354,31 @@
     </row>
     <row r="82" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A82" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="B82" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C82" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D82" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D82" s="12" t="s">
+      <c r="E82" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E82" s="12" t="s">
+      <c r="F82" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F82" s="12" t="s">
+      <c r="G82" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G82" s="11" t="s">
-        <v>135</v>
-      </c>
       <c r="H82" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I82" s="13">
-        <v>956</v>
+        <v>982</v>
       </c>
       <c r="J82" s="14" t="s">
         <v>28</v>
@@ -5440,31 +5386,31 @@
     </row>
     <row r="83" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A83" s="4" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="B83" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C83" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D83" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D83" s="6" t="s">
+      <c r="E83" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E83" s="6" t="s">
+      <c r="F83" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F83" s="6" t="s">
+      <c r="G83" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G83" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="H83" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I83" s="8">
-        <v>392</v>
+        <v>723</v>
       </c>
       <c r="J83" s="9" t="s">
         <v>20</v>
@@ -5472,31 +5418,31 @@
     </row>
     <row r="84" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A84" s="10" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="B84" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C84" s="12" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D84" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F84" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G84" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G84" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H84" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I84" s="13">
-        <v>986</v>
+        <v>974</v>
       </c>
       <c r="J84" s="16" t="s">
         <v>86</v>
@@ -5504,31 +5450,31 @@
     </row>
     <row r="85" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A85" s="4" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="B85" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C85" s="6" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E85" s="6" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="F85" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G85" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G85" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H85" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I85" s="8">
-        <v>182</v>
+        <v>700</v>
       </c>
       <c r="J85" s="9" t="s">
         <v>20</v>
@@ -5536,31 +5482,31 @@
     </row>
     <row r="86" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A86" s="10" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="B86" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C86" s="12" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="D86" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="F86" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G86" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G86" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H86" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I86" s="13">
-        <v>190</v>
+        <v>469</v>
       </c>
       <c r="J86" s="14" t="s">
         <v>28</v>
@@ -5568,31 +5514,31 @@
     </row>
     <row r="87" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A87" s="4" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="B87" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C87" s="6" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E87" s="6" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="F87" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G87" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G87" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H87" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I87" s="8">
-        <v>526</v>
+        <v>957</v>
       </c>
       <c r="J87" s="9" t="s">
         <v>20</v>
@@ -5600,31 +5546,31 @@
     </row>
     <row r="88" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A88" s="10" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="B88" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C88" s="12" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="D88" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="F88" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G88" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G88" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H88" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I88" s="13">
-        <v>856</v>
+        <v>429</v>
       </c>
       <c r="J88" s="15" t="s">
         <v>43</v>
@@ -5632,31 +5578,31 @@
     </row>
     <row r="89" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A89" s="4" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="B89" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C89" s="6" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="D89" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E89" s="6" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="F89" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G89" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G89" s="5" t="s">
-        <v>297</v>
-      </c>
-      <c r="H89" s="16" t="s">
-        <v>129</v>
+      <c r="H89" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I89" s="8">
-        <v>456</v>
+        <v>339</v>
       </c>
       <c r="J89" s="9" t="s">
         <v>20</v>
@@ -5664,31 +5610,31 @@
     </row>
     <row r="90" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A90" s="10" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C90" s="12" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="D90" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
       <c r="F90" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G90" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G90" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H90" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I90" s="13">
-        <v>691</v>
+        <v>955</v>
       </c>
       <c r="J90" s="14" t="s">
         <v>28</v>
@@ -5696,31 +5642,31 @@
     </row>
     <row r="91" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A91" s="4" t="s">
-        <v>301</v>
+        <v>295</v>
       </c>
       <c r="B91" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C91" s="6" t="s">
-        <v>302</v>
+        <v>296</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E91" s="6" t="s">
-        <v>303</v>
+        <v>297</v>
       </c>
       <c r="F91" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G91" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G91" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H91" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I91" s="8">
-        <v>892</v>
+        <v>844</v>
       </c>
       <c r="J91" s="9" t="s">
         <v>20</v>
@@ -5728,31 +5674,31 @@
     </row>
     <row r="92" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A92" s="10" t="s">
-        <v>304</v>
+        <v>298</v>
       </c>
       <c r="B92" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C92" s="12" t="s">
-        <v>305</v>
+        <v>299</v>
       </c>
       <c r="D92" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>306</v>
+        <v>300</v>
       </c>
       <c r="F92" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G92" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G92" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H92" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I92" s="13">
-        <v>294</v>
+        <v>638</v>
       </c>
       <c r="J92" s="15" t="s">
         <v>43</v>
@@ -5760,31 +5706,31 @@
     </row>
     <row r="93" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A93" s="4" t="s">
-        <v>307</v>
+        <v>301</v>
       </c>
       <c r="B93" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C93" s="6" t="s">
-        <v>308</v>
+        <v>302</v>
       </c>
       <c r="D93" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E93" s="6" t="s">
-        <v>309</v>
+        <v>303</v>
       </c>
       <c r="F93" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G93" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G93" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H93" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I93" s="8">
-        <v>783</v>
+        <v>826</v>
       </c>
       <c r="J93" s="9" t="s">
         <v>20</v>
@@ -5792,31 +5738,31 @@
     </row>
     <row r="94" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A94" s="10" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
       <c r="B94" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C94" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D94" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="D94" s="12" t="s">
+      <c r="E94" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E94" s="12" t="s">
+      <c r="F94" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="F94" s="12" t="s">
+      <c r="G94" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="G94" s="12" t="s">
-        <v>189</v>
-      </c>
       <c r="H94" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I94" s="13">
-        <v>565</v>
+        <v>709</v>
       </c>
       <c r="J94" s="16" t="s">
         <v>86</v>
@@ -5824,7 +5770,7 @@
     </row>
     <row r="95" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A95" s="4" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="B95" s="5" t="s">
         <v>13</v>
@@ -5848,7 +5794,7 @@
         <v>19</v>
       </c>
       <c r="I95" s="8">
-        <v>657</v>
+        <v>211</v>
       </c>
       <c r="J95" s="9" t="s">
         <v>20</v>
@@ -5856,7 +5802,7 @@
     </row>
     <row r="96" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A96" s="10" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
       <c r="B96" s="11" t="s">
         <v>22</v>
@@ -5880,7 +5826,7 @@
         <v>19</v>
       </c>
       <c r="I96" s="13">
-        <v>965</v>
+        <v>392</v>
       </c>
       <c r="J96" s="15" t="s">
         <v>43</v>
@@ -5888,7 +5834,7 @@
     </row>
     <row r="97" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A97" s="4" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="B97" s="5" t="s">
         <v>30</v>
@@ -5912,7 +5858,7 @@
         <v>19</v>
       </c>
       <c r="I97" s="8">
-        <v>526</v>
+        <v>502</v>
       </c>
       <c r="J97" s="9" t="s">
         <v>20</v>
@@ -5920,7 +5866,7 @@
     </row>
     <row r="98" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A98" s="10" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="B98" s="12" t="s">
         <v>37</v>
@@ -5944,7 +5890,7 @@
         <v>19</v>
       </c>
       <c r="I98" s="13">
-        <v>992</v>
+        <v>425</v>
       </c>
       <c r="J98" s="14" t="s">
         <v>28</v>
@@ -5952,7 +5898,7 @@
     </row>
     <row r="99" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A99" s="4" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="B99" s="5" t="s">
         <v>45</v>
@@ -5976,7 +5922,7 @@
         <v>19</v>
       </c>
       <c r="I99" s="8">
-        <v>481</v>
+        <v>225</v>
       </c>
       <c r="J99" s="9" t="s">
         <v>20</v>
@@ -5984,7 +5930,7 @@
     </row>
     <row r="100" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A100" s="10" t="s">
-        <v>316</v>
+        <v>310</v>
       </c>
       <c r="B100" s="11" t="s">
         <v>52</v>
@@ -6008,7 +5954,7 @@
         <v>19</v>
       </c>
       <c r="I100" s="13">
-        <v>671</v>
+        <v>605</v>
       </c>
       <c r="J100" s="15" t="s">
         <v>43</v>
@@ -6016,7 +5962,7 @@
     </row>
     <row r="101" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A101" s="4" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="B101" s="6" t="s">
         <v>59</v>
@@ -6040,7 +5986,7 @@
         <v>19</v>
       </c>
       <c r="I101" s="8">
-        <v>506</v>
+        <v>710</v>
       </c>
       <c r="J101" s="9" t="s">
         <v>20</v>
@@ -6048,7 +5994,7 @@
     </row>
     <row r="102" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A102" s="10" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
       <c r="B102" s="12" t="s">
         <v>66</v>
@@ -6072,7 +6018,7 @@
         <v>19</v>
       </c>
       <c r="I102" s="13">
-        <v>983</v>
+        <v>877</v>
       </c>
       <c r="J102" s="14" t="s">
         <v>28</v>
@@ -6080,7 +6026,7 @@
     </row>
     <row r="103" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A103" s="4" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="B103" s="6" t="s">
         <v>73</v>
@@ -6104,7 +6050,7 @@
         <v>19</v>
       </c>
       <c r="I103" s="8">
-        <v>471</v>
+        <v>346</v>
       </c>
       <c r="J103" s="9" t="s">
         <v>20</v>
@@ -6112,22 +6058,22 @@
     </row>
     <row r="104" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A104" s="10" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="B104" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C104" s="12" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
       <c r="D104" s="12" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="E104" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F104" s="12" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="G104" s="12" t="s">
         <v>85</v>
@@ -6136,7 +6082,7 @@
         <v>19</v>
       </c>
       <c r="I104" s="13">
-        <v>855</v>
+        <v>570</v>
       </c>
       <c r="J104" s="16" t="s">
         <v>86</v>
@@ -6144,7 +6090,7 @@
     </row>
     <row r="105" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A105" s="4" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="B105" s="5" t="s">
         <v>13</v>
@@ -6168,7 +6114,7 @@
         <v>19</v>
       </c>
       <c r="I105" s="8">
-        <v>665</v>
+        <v>823</v>
       </c>
       <c r="J105" s="9" t="s">
         <v>20</v>
@@ -6176,7 +6122,7 @@
     </row>
     <row r="106" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A106" s="10" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="B106" s="11" t="s">
         <v>22</v>
@@ -6194,13 +6140,13 @@
         <v>97</v>
       </c>
       <c r="G106" s="12" t="s">
-        <v>326</v>
-      </c>
-      <c r="H106" s="16" t="s">
-        <v>129</v>
+        <v>98</v>
+      </c>
+      <c r="H106" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I106" s="13">
-        <v>716</v>
+        <v>887</v>
       </c>
       <c r="J106" s="14" t="s">
         <v>28</v>
@@ -6208,7 +6154,7 @@
     </row>
     <row r="107" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A107" s="4" t="s">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="B107" s="5" t="s">
         <v>30</v>
@@ -6232,7 +6178,7 @@
         <v>19</v>
       </c>
       <c r="I107" s="8">
-        <v>887</v>
+        <v>276</v>
       </c>
       <c r="J107" s="9" t="s">
         <v>20</v>
@@ -6240,7 +6186,7 @@
     </row>
     <row r="108" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A108" s="10" t="s">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="B108" s="12" t="s">
         <v>37</v>
@@ -6264,7 +6210,7 @@
         <v>19</v>
       </c>
       <c r="I108" s="13">
-        <v>987</v>
+        <v>785</v>
       </c>
       <c r="J108" s="15" t="s">
         <v>43</v>
@@ -6272,7 +6218,7 @@
     </row>
     <row r="109" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A109" s="4" t="s">
-        <v>329</v>
+        <v>322</v>
       </c>
       <c r="B109" s="5" t="s">
         <v>45</v>
@@ -6296,7 +6242,7 @@
         <v>19</v>
       </c>
       <c r="I109" s="8">
-        <v>535</v>
+        <v>189</v>
       </c>
       <c r="J109" s="9" t="s">
         <v>20</v>
@@ -6304,7 +6250,7 @@
     </row>
     <row r="110" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A110" s="10" t="s">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B110" s="11" t="s">
         <v>52</v>
@@ -6328,7 +6274,7 @@
         <v>19</v>
       </c>
       <c r="I110" s="13">
-        <v>560</v>
+        <v>345</v>
       </c>
       <c r="J110" s="14" t="s">
         <v>28</v>
@@ -6336,7 +6282,7 @@
     </row>
     <row r="111" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A111" s="4" t="s">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="B111" s="6" t="s">
         <v>59</v>
@@ -6354,13 +6300,13 @@
         <v>127</v>
       </c>
       <c r="G111" s="6" t="s">
-        <v>216</v>
+        <v>128</v>
       </c>
       <c r="H111" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I111" s="8">
-        <v>386</v>
+        <v>403</v>
       </c>
       <c r="J111" s="9" t="s">
         <v>20</v>
@@ -6368,31 +6314,31 @@
     </row>
     <row r="112" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A112" s="10" t="s">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="B112" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C112" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D112" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D112" s="12" t="s">
+      <c r="E112" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E112" s="12" t="s">
+      <c r="F112" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F112" s="12" t="s">
+      <c r="G112" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G112" s="11" t="s">
-        <v>135</v>
-      </c>
       <c r="H112" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I112" s="13">
-        <v>691</v>
+        <v>700</v>
       </c>
       <c r="J112" s="15" t="s">
         <v>43</v>
@@ -6400,31 +6346,31 @@
     </row>
     <row r="113" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A113" s="4" t="s">
-        <v>333</v>
+        <v>326</v>
       </c>
       <c r="B113" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C113" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D113" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D113" s="6" t="s">
+      <c r="E113" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E113" s="6" t="s">
+      <c r="F113" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F113" s="6" t="s">
+      <c r="G113" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G113" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="H113" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I113" s="8">
-        <v>497</v>
+        <v>331</v>
       </c>
       <c r="J113" s="9" t="s">
         <v>20</v>
@@ -6432,31 +6378,31 @@
     </row>
     <row r="114" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A114" s="10" t="s">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="B114" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C114" s="12" t="s">
-        <v>335</v>
+        <v>328</v>
       </c>
       <c r="D114" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E114" s="12" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="F114" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G114" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G114" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H114" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I114" s="13">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="J114" s="16" t="s">
         <v>86</v>
@@ -6464,31 +6410,31 @@
     </row>
     <row r="115" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A115" s="4" t="s">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="B115" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C115" s="6" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="D115" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E115" s="6" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="F115" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G115" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G115" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H115" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I115" s="8">
-        <v>937</v>
+        <v>322</v>
       </c>
       <c r="J115" s="9" t="s">
         <v>20</v>
@@ -6496,31 +6442,31 @@
     </row>
     <row r="116" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A116" s="10" t="s">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B116" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C116" s="12" t="s">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="D116" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E116" s="12" t="s">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="F116" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G116" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G116" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H116" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I116" s="13">
-        <v>905</v>
+        <v>611</v>
       </c>
       <c r="J116" s="15" t="s">
         <v>43</v>
@@ -6528,31 +6474,31 @@
     </row>
     <row r="117" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A117" s="4" t="s">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="B117" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C117" s="6" t="s">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="D117" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E117" s="6" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="F117" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G117" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G117" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H117" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I117" s="8">
-        <v>802</v>
+        <v>982</v>
       </c>
       <c r="J117" s="9" t="s">
         <v>20</v>
@@ -6560,31 +6506,31 @@
     </row>
     <row r="118" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A118" s="10" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="B118" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C118" s="12" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="D118" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E118" s="12" t="s">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="F118" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G118" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G118" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H118" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I118" s="13">
-        <v>556</v>
+        <v>222</v>
       </c>
       <c r="J118" s="14" t="s">
         <v>28</v>
@@ -6592,31 +6538,31 @@
     </row>
     <row r="119" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A119" s="4" t="s">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="B119" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C119" s="6" t="s">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E119" s="6" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="F119" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G119" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G119" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H119" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I119" s="8">
-        <v>373</v>
+        <v>265</v>
       </c>
       <c r="J119" s="9" t="s">
         <v>20</v>
@@ -6624,31 +6570,31 @@
     </row>
     <row r="120" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A120" s="10" t="s">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="B120" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C120" s="12" t="s">
-        <v>353</v>
+        <v>346</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E120" s="12" t="s">
-        <v>354</v>
+        <v>347</v>
       </c>
       <c r="F120" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G120" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G120" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H120" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I120" s="13">
-        <v>866</v>
+        <v>290</v>
       </c>
       <c r="J120" s="15" t="s">
         <v>43</v>
@@ -6656,31 +6602,31 @@
     </row>
     <row r="121" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A121" s="4" t="s">
-        <v>355</v>
+        <v>348</v>
       </c>
       <c r="B121" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>356</v>
+        <v>349</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E121" s="6" t="s">
-        <v>357</v>
+        <v>350</v>
       </c>
       <c r="F121" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G121" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G121" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H121" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I121" s="8">
-        <v>605</v>
+        <v>901</v>
       </c>
       <c r="J121" s="9" t="s">
         <v>20</v>
@@ -6688,31 +6634,31 @@
     </row>
     <row r="122" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A122" s="10" t="s">
-        <v>358</v>
+        <v>351</v>
       </c>
       <c r="B122" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C122" s="12" t="s">
-        <v>359</v>
+        <v>352</v>
       </c>
       <c r="D122" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E122" s="12" t="s">
-        <v>360</v>
+        <v>353</v>
       </c>
       <c r="F122" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G122" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G122" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H122" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I122" s="13">
-        <v>210</v>
+        <v>347</v>
       </c>
       <c r="J122" s="14" t="s">
         <v>28</v>
@@ -6720,31 +6666,31 @@
     </row>
     <row r="123" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A123" s="4" t="s">
-        <v>361</v>
+        <v>354</v>
       </c>
       <c r="B123" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C123" s="6" t="s">
-        <v>362</v>
+        <v>355</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E123" s="6" t="s">
-        <v>363</v>
+        <v>356</v>
       </c>
       <c r="F123" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G123" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G123" s="5" t="s">
-        <v>364</v>
-      </c>
-      <c r="H123" s="16" t="s">
-        <v>129</v>
+      <c r="H123" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I123" s="8">
-        <v>524</v>
+        <v>834</v>
       </c>
       <c r="J123" s="9" t="s">
         <v>20</v>
@@ -6752,31 +6698,31 @@
     </row>
     <row r="124" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A124" s="10" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
       <c r="B124" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C124" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D124" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="D124" s="12" t="s">
+      <c r="E124" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E124" s="12" t="s">
+      <c r="F124" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="F124" s="12" t="s">
+      <c r="G124" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="G124" s="12" t="s">
-        <v>189</v>
-      </c>
       <c r="H124" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I124" s="13">
-        <v>868</v>
+        <v>989</v>
       </c>
       <c r="J124" s="16" t="s">
         <v>86</v>
@@ -6784,7 +6730,7 @@
     </row>
     <row r="125" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A125" s="4" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="B125" s="5" t="s">
         <v>13</v>
@@ -6808,7 +6754,7 @@
         <v>19</v>
       </c>
       <c r="I125" s="8">
-        <v>606</v>
+        <v>976</v>
       </c>
       <c r="J125" s="9" t="s">
         <v>20</v>
@@ -6816,7 +6762,7 @@
     </row>
     <row r="126" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A126" s="10" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
       <c r="B126" s="11" t="s">
         <v>22</v>
@@ -6840,7 +6786,7 @@
         <v>19</v>
       </c>
       <c r="I126" s="13">
-        <v>898</v>
+        <v>510</v>
       </c>
       <c r="J126" s="14" t="s">
         <v>28</v>
@@ -6848,7 +6794,7 @@
     </row>
     <row r="127" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A127" s="4" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="B127" s="5" t="s">
         <v>30</v>
@@ -6872,7 +6818,7 @@
         <v>19</v>
       </c>
       <c r="I127" s="8">
-        <v>780</v>
+        <v>934</v>
       </c>
       <c r="J127" s="9" t="s">
         <v>20</v>
@@ -6880,22 +6826,22 @@
     </row>
     <row r="128" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A128" s="10" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
       <c r="B128" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C128" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D128" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E128" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F128" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="F128" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="G128" s="12" t="s">
         <v>42</v>
@@ -6904,7 +6850,7 @@
         <v>19</v>
       </c>
       <c r="I128" s="13">
-        <v>747</v>
+        <v>199</v>
       </c>
       <c r="J128" s="15" t="s">
         <v>43</v>
@@ -6912,7 +6858,7 @@
     </row>
     <row r="129" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" s="4" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="B129" s="5" t="s">
         <v>45</v>
@@ -6936,7 +6882,7 @@
         <v>19</v>
       </c>
       <c r="I129" s="8">
-        <v>451</v>
+        <v>342</v>
       </c>
       <c r="J129" s="9" t="s">
         <v>20</v>
@@ -6944,7 +6890,7 @@
     </row>
     <row r="130" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" s="10" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
       <c r="B130" s="11" t="s">
         <v>52</v>
@@ -6968,7 +6914,7 @@
         <v>19</v>
       </c>
       <c r="I130" s="13">
-        <v>703</v>
+        <v>554</v>
       </c>
       <c r="J130" s="14" t="s">
         <v>28</v>
@@ -6976,7 +6922,7 @@
     </row>
     <row r="131" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" s="4" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="B131" s="6" t="s">
         <v>59</v>
@@ -7000,7 +6946,7 @@
         <v>19</v>
       </c>
       <c r="I131" s="8">
-        <v>999</v>
+        <v>222</v>
       </c>
       <c r="J131" s="9" t="s">
         <v>20</v>
@@ -7008,7 +6954,7 @@
     </row>
     <row r="132" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" s="10" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
       <c r="B132" s="12" t="s">
         <v>66</v>
@@ -7032,7 +6978,7 @@
         <v>19</v>
       </c>
       <c r="I132" s="13">
-        <v>328</v>
+        <v>194</v>
       </c>
       <c r="J132" s="15" t="s">
         <v>43</v>
@@ -7040,7 +6986,7 @@
     </row>
     <row r="133" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A133" s="4" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="B133" s="6" t="s">
         <v>73</v>
@@ -7064,7 +7010,7 @@
         <v>19</v>
       </c>
       <c r="I133" s="8">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="J133" s="9" t="s">
         <v>20</v>
@@ -7072,22 +7018,22 @@
     </row>
     <row r="134" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A134" s="10" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="B134" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C134" s="12" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="D134" s="12" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="E134" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F134" s="12" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="G134" s="12" t="s">
         <v>85</v>
@@ -7096,7 +7042,7 @@
         <v>19</v>
       </c>
       <c r="I134" s="13">
-        <v>954</v>
+        <v>393</v>
       </c>
       <c r="J134" s="16" t="s">
         <v>86</v>
@@ -7104,13 +7050,13 @@
     </row>
     <row r="135" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A135" s="4" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="B135" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C135" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D135" s="6" t="s">
         <v>89</v>
@@ -7119,7 +7065,7 @@
         <v>90</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G135" s="6" t="s">
         <v>92</v>
@@ -7128,7 +7074,7 @@
         <v>19</v>
       </c>
       <c r="I135" s="8">
-        <v>337</v>
+        <v>363</v>
       </c>
       <c r="J135" s="9" t="s">
         <v>20</v>
@@ -7136,7 +7082,7 @@
     </row>
     <row r="136" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A136" s="10" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="B136" s="11" t="s">
         <v>22</v>
@@ -7160,7 +7106,7 @@
         <v>19</v>
       </c>
       <c r="I136" s="13">
-        <v>497</v>
+        <v>527</v>
       </c>
       <c r="J136" s="15" t="s">
         <v>43</v>
@@ -7168,7 +7114,7 @@
     </row>
     <row r="137" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A137" s="4" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="B137" s="5" t="s">
         <v>30</v>
@@ -7192,7 +7138,7 @@
         <v>19</v>
       </c>
       <c r="I137" s="8">
-        <v>847</v>
+        <v>933</v>
       </c>
       <c r="J137" s="9" t="s">
         <v>20</v>
@@ -7200,7 +7146,7 @@
     </row>
     <row r="138" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A138" s="10" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="B138" s="12" t="s">
         <v>37</v>
@@ -7224,7 +7170,7 @@
         <v>19</v>
       </c>
       <c r="I138" s="13">
-        <v>568</v>
+        <v>944</v>
       </c>
       <c r="J138" s="14" t="s">
         <v>28</v>
@@ -7232,7 +7178,7 @@
     </row>
     <row r="139" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A139" s="4" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="B139" s="5" t="s">
         <v>45</v>
@@ -7256,7 +7202,7 @@
         <v>19</v>
       </c>
       <c r="I139" s="8">
-        <v>270</v>
+        <v>726</v>
       </c>
       <c r="J139" s="9" t="s">
         <v>20</v>
@@ -7264,7 +7210,7 @@
     </row>
     <row r="140" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A140" s="10" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="B140" s="11" t="s">
         <v>52</v>
@@ -7282,13 +7228,13 @@
         <v>121</v>
       </c>
       <c r="G140" s="12" t="s">
-        <v>385</v>
-      </c>
-      <c r="H140" s="16" t="s">
-        <v>129</v>
+        <v>122</v>
+      </c>
+      <c r="H140" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I140" s="13">
-        <v>453</v>
+        <v>781</v>
       </c>
       <c r="J140" s="15" t="s">
         <v>43</v>
@@ -7296,7 +7242,7 @@
     </row>
     <row r="141" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A141" s="4" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="B141" s="6" t="s">
         <v>59</v>
@@ -7314,13 +7260,13 @@
         <v>127</v>
       </c>
       <c r="G141" s="6" t="s">
-        <v>216</v>
+        <v>128</v>
       </c>
       <c r="H141" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I141" s="8">
-        <v>437</v>
+        <v>683</v>
       </c>
       <c r="J141" s="9" t="s">
         <v>20</v>
@@ -7328,31 +7274,31 @@
     </row>
     <row r="142" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A142" s="10" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="B142" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C142" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D142" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D142" s="12" t="s">
+      <c r="E142" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E142" s="12" t="s">
+      <c r="F142" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F142" s="12" t="s">
+      <c r="G142" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G142" s="11" t="s">
-        <v>135</v>
-      </c>
       <c r="H142" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I142" s="13">
-        <v>903</v>
+        <v>279</v>
       </c>
       <c r="J142" s="14" t="s">
         <v>28</v>
@@ -7360,31 +7306,31 @@
     </row>
     <row r="143" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A143" s="4" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
       <c r="B143" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C143" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D143" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D143" s="6" t="s">
+      <c r="E143" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E143" s="6" t="s">
+      <c r="F143" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F143" s="6" t="s">
+      <c r="G143" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G143" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="H143" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I143" s="8">
-        <v>564</v>
+        <v>357</v>
       </c>
       <c r="J143" s="9" t="s">
         <v>20</v>
@@ -7392,31 +7338,31 @@
     </row>
     <row r="144" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A144" s="10" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="B144" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C144" s="12" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="D144" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E144" s="12" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="F144" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G144" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G144" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H144" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I144" s="13">
-        <v>370</v>
+        <v>793</v>
       </c>
       <c r="J144" s="16" t="s">
         <v>86</v>
@@ -7424,31 +7370,31 @@
     </row>
     <row r="145" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A145" s="4" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="B145" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C145" s="6" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E145" s="6" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="F145" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G145" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G145" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H145" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I145" s="8">
-        <v>795</v>
+        <v>837</v>
       </c>
       <c r="J145" s="9" t="s">
         <v>20</v>
@@ -7456,31 +7402,31 @@
     </row>
     <row r="146" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A146" s="10" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
       <c r="B146" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C146" s="12" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="D146" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E146" s="12" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
       <c r="F146" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G146" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G146" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H146" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I146" s="13">
-        <v>647</v>
+        <v>312</v>
       </c>
       <c r="J146" s="14" t="s">
         <v>28</v>
@@ -7488,31 +7434,31 @@
     </row>
     <row r="147" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A147" s="4" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="B147" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C147" s="6" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="D147" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E147" s="6" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
       <c r="F147" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G147" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G147" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H147" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I147" s="8">
-        <v>953</v>
+        <v>430</v>
       </c>
       <c r="J147" s="9" t="s">
         <v>20</v>
@@ -7520,31 +7466,31 @@
     </row>
     <row r="148" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A148" s="10" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="B148" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C148" s="12" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
       <c r="D148" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E148" s="12" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="F148" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G148" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G148" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H148" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I148" s="13">
-        <v>697</v>
+        <v>655</v>
       </c>
       <c r="J148" s="15" t="s">
         <v>43</v>
@@ -7552,31 +7498,31 @@
     </row>
     <row r="149" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A149" s="4" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
       <c r="B149" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C149" s="6" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="D149" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E149" s="6" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
       <c r="F149" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G149" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G149" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H149" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I149" s="8">
-        <v>564</v>
+        <v>855</v>
       </c>
       <c r="J149" s="9" t="s">
         <v>20</v>
@@ -7584,31 +7530,31 @@
     </row>
     <row r="150" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A150" s="10" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="B150" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C150" s="12" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
       <c r="D150" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E150" s="12" t="s">
-        <v>409</v>
+        <v>400</v>
       </c>
       <c r="F150" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G150" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G150" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H150" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I150" s="13">
-        <v>898</v>
+        <v>828</v>
       </c>
       <c r="J150" s="14" t="s">
         <v>28</v>
@@ -7616,31 +7562,31 @@
     </row>
     <row r="151" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A151" s="4" t="s">
-        <v>410</v>
+        <v>401</v>
       </c>
       <c r="B151" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C151" s="6" t="s">
-        <v>411</v>
+        <v>402</v>
       </c>
       <c r="D151" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E151" s="6" t="s">
-        <v>412</v>
+        <v>403</v>
       </c>
       <c r="F151" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G151" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G151" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H151" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I151" s="8">
-        <v>755</v>
+        <v>799</v>
       </c>
       <c r="J151" s="9" t="s">
         <v>20</v>
@@ -7648,31 +7594,31 @@
     </row>
     <row r="152" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A152" s="10" t="s">
-        <v>413</v>
+        <v>404</v>
       </c>
       <c r="B152" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C152" s="12" t="s">
-        <v>414</v>
+        <v>405</v>
       </c>
       <c r="D152" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E152" s="12" t="s">
-        <v>415</v>
+        <v>406</v>
       </c>
       <c r="F152" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G152" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G152" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H152" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I152" s="13">
-        <v>560</v>
+        <v>567</v>
       </c>
       <c r="J152" s="15" t="s">
         <v>43</v>
@@ -7680,31 +7626,31 @@
     </row>
     <row r="153" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A153" s="4" t="s">
-        <v>416</v>
+        <v>407</v>
       </c>
       <c r="B153" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C153" s="6" t="s">
-        <v>417</v>
+        <v>408</v>
       </c>
       <c r="D153" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E153" s="6" t="s">
-        <v>418</v>
+        <v>409</v>
       </c>
       <c r="F153" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G153" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G153" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H153" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I153" s="8">
-        <v>602</v>
+        <v>232</v>
       </c>
       <c r="J153" s="9" t="s">
         <v>20</v>
@@ -7712,31 +7658,31 @@
     </row>
     <row r="154" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A154" s="10" t="s">
-        <v>419</v>
+        <v>410</v>
       </c>
       <c r="B154" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C154" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D154" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="D154" s="12" t="s">
+      <c r="E154" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E154" s="12" t="s">
+      <c r="F154" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="F154" s="12" t="s">
+      <c r="G154" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="G154" s="12" t="s">
-        <v>189</v>
-      </c>
       <c r="H154" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I154" s="13">
-        <v>784</v>
+        <v>353</v>
       </c>
       <c r="J154" s="16" t="s">
         <v>86</v>
@@ -7744,7 +7690,7 @@
     </row>
     <row r="155" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A155" s="4" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="B155" s="5" t="s">
         <v>13</v>
@@ -7768,7 +7714,7 @@
         <v>19</v>
       </c>
       <c r="I155" s="8">
-        <v>992</v>
+        <v>859</v>
       </c>
       <c r="J155" s="9" t="s">
         <v>20</v>
@@ -7776,7 +7722,7 @@
     </row>
     <row r="156" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A156" s="10" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="B156" s="11" t="s">
         <v>22</v>
@@ -7800,7 +7746,7 @@
         <v>19</v>
       </c>
       <c r="I156" s="13">
-        <v>915</v>
+        <v>865</v>
       </c>
       <c r="J156" s="15" t="s">
         <v>43</v>
@@ -7808,7 +7754,7 @@
     </row>
     <row r="157" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A157" s="4" t="s">
-        <v>422</v>
+        <v>413</v>
       </c>
       <c r="B157" s="5" t="s">
         <v>30</v>
@@ -7826,13 +7772,13 @@
         <v>34</v>
       </c>
       <c r="G157" s="6" t="s">
-        <v>423</v>
-      </c>
-      <c r="H157" s="16" t="s">
-        <v>129</v>
+        <v>35</v>
+      </c>
+      <c r="H157" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I157" s="8">
-        <v>485</v>
+        <v>525</v>
       </c>
       <c r="J157" s="9" t="s">
         <v>20</v>
@@ -7840,22 +7786,22 @@
     </row>
     <row r="158" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A158" s="10" t="s">
-        <v>424</v>
+        <v>414</v>
       </c>
       <c r="B158" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C158" s="12" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D158" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E158" s="12" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F158" s="12" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G158" s="12" t="s">
         <v>42</v>
@@ -7864,7 +7810,7 @@
         <v>19</v>
       </c>
       <c r="I158" s="13">
-        <v>697</v>
+        <v>207</v>
       </c>
       <c r="J158" s="14" t="s">
         <v>28</v>
@@ -7872,7 +7818,7 @@
     </row>
     <row r="159" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A159" s="4" t="s">
-        <v>425</v>
+        <v>415</v>
       </c>
       <c r="B159" s="5" t="s">
         <v>45</v>
@@ -7896,7 +7842,7 @@
         <v>19</v>
       </c>
       <c r="I159" s="8">
-        <v>988</v>
+        <v>546</v>
       </c>
       <c r="J159" s="9" t="s">
         <v>20</v>
@@ -7904,7 +7850,7 @@
     </row>
     <row r="160" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A160" s="10" t="s">
-        <v>426</v>
+        <v>416</v>
       </c>
       <c r="B160" s="11" t="s">
         <v>52</v>
@@ -7928,7 +7874,7 @@
         <v>19</v>
       </c>
       <c r="I160" s="13">
-        <v>530</v>
+        <v>514</v>
       </c>
       <c r="J160" s="15" t="s">
         <v>43</v>
@@ -7936,7 +7882,7 @@
     </row>
     <row r="161" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A161" s="4" t="s">
-        <v>427</v>
+        <v>417</v>
       </c>
       <c r="B161" s="6" t="s">
         <v>59</v>
@@ -7960,7 +7906,7 @@
         <v>19</v>
       </c>
       <c r="I161" s="8">
-        <v>922</v>
+        <v>660</v>
       </c>
       <c r="J161" s="9" t="s">
         <v>20</v>
@@ -7968,7 +7914,7 @@
     </row>
     <row r="162" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A162" s="10" t="s">
-        <v>428</v>
+        <v>418</v>
       </c>
       <c r="B162" s="12" t="s">
         <v>66</v>
@@ -7992,7 +7938,7 @@
         <v>19</v>
       </c>
       <c r="I162" s="13">
-        <v>716</v>
+        <v>516</v>
       </c>
       <c r="J162" s="14" t="s">
         <v>28</v>
@@ -8000,7 +7946,7 @@
     </row>
     <row r="163" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A163" s="4" t="s">
-        <v>429</v>
+        <v>419</v>
       </c>
       <c r="B163" s="6" t="s">
         <v>73</v>
@@ -8024,7 +7970,7 @@
         <v>19</v>
       </c>
       <c r="I163" s="8">
-        <v>271</v>
+        <v>232</v>
       </c>
       <c r="J163" s="9" t="s">
         <v>20</v>
@@ -8032,22 +7978,22 @@
     </row>
     <row r="164" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A164" s="10" t="s">
-        <v>430</v>
+        <v>420</v>
       </c>
       <c r="B164" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C164" s="12" t="s">
-        <v>431</v>
+        <v>421</v>
       </c>
       <c r="D164" s="12" t="s">
-        <v>432</v>
+        <v>422</v>
       </c>
       <c r="E164" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F164" s="12" t="s">
-        <v>433</v>
+        <v>423</v>
       </c>
       <c r="G164" s="12" t="s">
         <v>85</v>
@@ -8056,7 +8002,7 @@
         <v>19</v>
       </c>
       <c r="I164" s="13">
-        <v>576</v>
+        <v>681</v>
       </c>
       <c r="J164" s="16" t="s">
         <v>86</v>
@@ -8064,13 +8010,13 @@
     </row>
     <row r="165" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A165" s="4" t="s">
-        <v>434</v>
+        <v>424</v>
       </c>
       <c r="B165" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C165" s="6" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D165" s="6" t="s">
         <v>89</v>
@@ -8079,7 +8025,7 @@
         <v>90</v>
       </c>
       <c r="F165" s="6" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G165" s="6" t="s">
         <v>92</v>
@@ -8088,7 +8034,7 @@
         <v>19</v>
       </c>
       <c r="I165" s="8">
-        <v>705</v>
+        <v>954</v>
       </c>
       <c r="J165" s="9" t="s">
         <v>20</v>
@@ -8096,7 +8042,7 @@
     </row>
     <row r="166" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A166" s="10" t="s">
-        <v>435</v>
+        <v>425</v>
       </c>
       <c r="B166" s="11" t="s">
         <v>22</v>
@@ -8120,7 +8066,7 @@
         <v>19</v>
       </c>
       <c r="I166" s="13">
-        <v>636</v>
+        <v>280</v>
       </c>
       <c r="J166" s="14" t="s">
         <v>28</v>
@@ -8128,7 +8074,7 @@
     </row>
     <row r="167" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A167" s="4" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="B167" s="5" t="s">
         <v>30</v>
@@ -8152,7 +8098,7 @@
         <v>19</v>
       </c>
       <c r="I167" s="8">
-        <v>292</v>
+        <v>760</v>
       </c>
       <c r="J167" s="9" t="s">
         <v>20</v>
@@ -8160,7 +8106,7 @@
     </row>
     <row r="168" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A168" s="10" t="s">
-        <v>437</v>
+        <v>427</v>
       </c>
       <c r="B168" s="12" t="s">
         <v>37</v>
@@ -8184,7 +8130,7 @@
         <v>19</v>
       </c>
       <c r="I168" s="13">
-        <v>710</v>
+        <v>477</v>
       </c>
       <c r="J168" s="15" t="s">
         <v>43</v>
@@ -8192,7 +8138,7 @@
     </row>
     <row r="169" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A169" s="4" t="s">
-        <v>438</v>
+        <v>428</v>
       </c>
       <c r="B169" s="5" t="s">
         <v>45</v>
@@ -8216,7 +8162,7 @@
         <v>19</v>
       </c>
       <c r="I169" s="8">
-        <v>180</v>
+        <v>826</v>
       </c>
       <c r="J169" s="9" t="s">
         <v>20</v>
@@ -8224,7 +8170,7 @@
     </row>
     <row r="170" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A170" s="10" t="s">
-        <v>439</v>
+        <v>429</v>
       </c>
       <c r="B170" s="11" t="s">
         <v>52</v>
@@ -8248,7 +8194,7 @@
         <v>19</v>
       </c>
       <c r="I170" s="13">
-        <v>922</v>
+        <v>841</v>
       </c>
       <c r="J170" s="14" t="s">
         <v>28</v>
@@ -8256,7 +8202,7 @@
     </row>
     <row r="171" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A171" s="4" t="s">
-        <v>440</v>
+        <v>430</v>
       </c>
       <c r="B171" s="6" t="s">
         <v>59</v>
@@ -8274,13 +8220,13 @@
         <v>127</v>
       </c>
       <c r="G171" s="6" t="s">
-        <v>216</v>
+        <v>128</v>
       </c>
       <c r="H171" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I171" s="8">
-        <v>483</v>
+        <v>804</v>
       </c>
       <c r="J171" s="9" t="s">
         <v>20</v>
@@ -8288,31 +8234,31 @@
     </row>
     <row r="172" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A172" s="10" t="s">
-        <v>441</v>
+        <v>431</v>
       </c>
       <c r="B172" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C172" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D172" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D172" s="12" t="s">
+      <c r="E172" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E172" s="12" t="s">
+      <c r="F172" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F172" s="12" t="s">
+      <c r="G172" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G172" s="11" t="s">
-        <v>135</v>
-      </c>
       <c r="H172" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I172" s="13">
-        <v>478</v>
+        <v>306</v>
       </c>
       <c r="J172" s="15" t="s">
         <v>43</v>
@@ -8320,31 +8266,31 @@
     </row>
     <row r="173" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A173" s="4" t="s">
-        <v>442</v>
+        <v>432</v>
       </c>
       <c r="B173" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C173" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D173" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D173" s="6" t="s">
+      <c r="E173" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E173" s="6" t="s">
+      <c r="F173" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F173" s="6" t="s">
+      <c r="G173" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G173" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="H173" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I173" s="8">
-        <v>880</v>
+        <v>214</v>
       </c>
       <c r="J173" s="9" t="s">
         <v>20</v>
@@ -8352,31 +8298,31 @@
     </row>
     <row r="174" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A174" s="10" t="s">
-        <v>443</v>
+        <v>433</v>
       </c>
       <c r="B174" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C174" s="12" t="s">
-        <v>444</v>
+        <v>434</v>
       </c>
       <c r="D174" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E174" s="12" t="s">
-        <v>445</v>
+        <v>435</v>
       </c>
       <c r="F174" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G174" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G174" s="11" t="s">
-        <v>446</v>
-      </c>
-      <c r="H174" s="16" t="s">
-        <v>129</v>
+      <c r="H174" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I174" s="13">
-        <v>199</v>
+        <v>661</v>
       </c>
       <c r="J174" s="16" t="s">
         <v>86</v>
@@ -8384,31 +8330,31 @@
     </row>
     <row r="175" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A175" s="4" t="s">
-        <v>447</v>
+        <v>436</v>
       </c>
       <c r="B175" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C175" s="6" t="s">
-        <v>448</v>
+        <v>437</v>
       </c>
       <c r="D175" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E175" s="6" t="s">
-        <v>449</v>
+        <v>438</v>
       </c>
       <c r="F175" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G175" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G175" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H175" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I175" s="8">
-        <v>652</v>
+        <v>365</v>
       </c>
       <c r="J175" s="9" t="s">
         <v>20</v>
@@ -8416,31 +8362,31 @@
     </row>
     <row r="176" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A176" s="10" t="s">
-        <v>450</v>
+        <v>439</v>
       </c>
       <c r="B176" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C176" s="12" t="s">
-        <v>451</v>
+        <v>440</v>
       </c>
       <c r="D176" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E176" s="12" t="s">
-        <v>452</v>
+        <v>441</v>
       </c>
       <c r="F176" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G176" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G176" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H176" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I176" s="13">
-        <v>216</v>
+        <v>757</v>
       </c>
       <c r="J176" s="15" t="s">
         <v>43</v>
@@ -8448,31 +8394,31 @@
     </row>
     <row r="177" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A177" s="4" t="s">
-        <v>453</v>
+        <v>442</v>
       </c>
       <c r="B177" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C177" s="6" t="s">
-        <v>454</v>
+        <v>443</v>
       </c>
       <c r="D177" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E177" s="6" t="s">
-        <v>455</v>
+        <v>444</v>
       </c>
       <c r="F177" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G177" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G177" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H177" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I177" s="8">
-        <v>841</v>
+        <v>671</v>
       </c>
       <c r="J177" s="9" t="s">
         <v>20</v>
@@ -8480,31 +8426,31 @@
     </row>
     <row r="178" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A178" s="10" t="s">
-        <v>456</v>
+        <v>445</v>
       </c>
       <c r="B178" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C178" s="12" t="s">
-        <v>457</v>
+        <v>446</v>
       </c>
       <c r="D178" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E178" s="12" t="s">
-        <v>458</v>
+        <v>447</v>
       </c>
       <c r="F178" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G178" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G178" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H178" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I178" s="13">
-        <v>732</v>
+        <v>556</v>
       </c>
       <c r="J178" s="14" t="s">
         <v>28</v>
@@ -8512,31 +8458,31 @@
     </row>
     <row r="179" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A179" s="4" t="s">
-        <v>459</v>
+        <v>448</v>
       </c>
       <c r="B179" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C179" s="6" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="D179" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E179" s="6" t="s">
-        <v>461</v>
+        <v>450</v>
       </c>
       <c r="F179" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G179" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G179" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H179" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I179" s="8">
-        <v>321</v>
+        <v>994</v>
       </c>
       <c r="J179" s="9" t="s">
         <v>20</v>
@@ -8544,31 +8490,31 @@
     </row>
     <row r="180" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A180" s="10" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="B180" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C180" s="12" t="s">
-        <v>463</v>
+        <v>452</v>
       </c>
       <c r="D180" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E180" s="12" t="s">
-        <v>464</v>
+        <v>453</v>
       </c>
       <c r="F180" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G180" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G180" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H180" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I180" s="13">
-        <v>948</v>
+        <v>400</v>
       </c>
       <c r="J180" s="15" t="s">
         <v>43</v>
@@ -8576,31 +8522,31 @@
     </row>
     <row r="181" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A181" s="4" t="s">
-        <v>465</v>
+        <v>454</v>
       </c>
       <c r="B181" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C181" s="6" t="s">
-        <v>466</v>
+        <v>455</v>
       </c>
       <c r="D181" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E181" s="6" t="s">
-        <v>467</v>
+        <v>456</v>
       </c>
       <c r="F181" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G181" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G181" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H181" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I181" s="8">
-        <v>448</v>
+        <v>258</v>
       </c>
       <c r="J181" s="9" t="s">
         <v>20</v>
@@ -8608,31 +8554,31 @@
     </row>
     <row r="182" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A182" s="10" t="s">
-        <v>468</v>
+        <v>457</v>
       </c>
       <c r="B182" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C182" s="12" t="s">
-        <v>469</v>
+        <v>458</v>
       </c>
       <c r="D182" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E182" s="12" t="s">
-        <v>470</v>
+        <v>459</v>
       </c>
       <c r="F182" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G182" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G182" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H182" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I182" s="13">
-        <v>301</v>
+        <v>791</v>
       </c>
       <c r="J182" s="14" t="s">
         <v>28</v>
@@ -8640,31 +8586,31 @@
     </row>
     <row r="183" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A183" s="4" t="s">
-        <v>471</v>
+        <v>460</v>
       </c>
       <c r="B183" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C183" s="6" t="s">
-        <v>472</v>
+        <v>461</v>
       </c>
       <c r="D183" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E183" s="6" t="s">
-        <v>473</v>
+        <v>462</v>
       </c>
       <c r="F183" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G183" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G183" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H183" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I183" s="8">
-        <v>546</v>
+        <v>337</v>
       </c>
       <c r="J183" s="9" t="s">
         <v>20</v>
@@ -8672,31 +8618,31 @@
     </row>
     <row r="184" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A184" s="10" t="s">
-        <v>474</v>
+        <v>463</v>
       </c>
       <c r="B184" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C184" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D184" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="D184" s="12" t="s">
+      <c r="E184" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E184" s="12" t="s">
+      <c r="F184" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="F184" s="12" t="s">
+      <c r="G184" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="G184" s="12" t="s">
-        <v>189</v>
-      </c>
       <c r="H184" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I184" s="13">
-        <v>856</v>
+        <v>257</v>
       </c>
       <c r="J184" s="16" t="s">
         <v>86</v>
@@ -8704,7 +8650,7 @@
     </row>
     <row r="185" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A185" s="4" t="s">
-        <v>475</v>
+        <v>464</v>
       </c>
       <c r="B185" s="5" t="s">
         <v>13</v>
@@ -8728,7 +8674,7 @@
         <v>19</v>
       </c>
       <c r="I185" s="8">
-        <v>263</v>
+        <v>635</v>
       </c>
       <c r="J185" s="9" t="s">
         <v>20</v>
@@ -8736,7 +8682,7 @@
     </row>
     <row r="186" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A186" s="10" t="s">
-        <v>476</v>
+        <v>465</v>
       </c>
       <c r="B186" s="11" t="s">
         <v>22</v>
@@ -8760,7 +8706,7 @@
         <v>19</v>
       </c>
       <c r="I186" s="13">
-        <v>256</v>
+        <v>187</v>
       </c>
       <c r="J186" s="14" t="s">
         <v>28</v>
@@ -8768,7 +8714,7 @@
     </row>
     <row r="187" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A187" s="4" t="s">
-        <v>477</v>
+        <v>466</v>
       </c>
       <c r="B187" s="5" t="s">
         <v>30</v>
@@ -8792,7 +8738,7 @@
         <v>19</v>
       </c>
       <c r="I187" s="8">
-        <v>719</v>
+        <v>812</v>
       </c>
       <c r="J187" s="9" t="s">
         <v>20</v>
@@ -8800,7 +8746,7 @@
     </row>
     <row r="188" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A188" s="10" t="s">
-        <v>478</v>
+        <v>467</v>
       </c>
       <c r="B188" s="12" t="s">
         <v>37</v>
@@ -8824,7 +8770,7 @@
         <v>19</v>
       </c>
       <c r="I188" s="13">
-        <v>983</v>
+        <v>441</v>
       </c>
       <c r="J188" s="15" t="s">
         <v>43</v>
@@ -8832,7 +8778,7 @@
     </row>
     <row r="189" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A189" s="4" t="s">
-        <v>479</v>
+        <v>468</v>
       </c>
       <c r="B189" s="5" t="s">
         <v>45</v>
@@ -8856,7 +8802,7 @@
         <v>19</v>
       </c>
       <c r="I189" s="8">
-        <v>651</v>
+        <v>349</v>
       </c>
       <c r="J189" s="9" t="s">
         <v>20</v>
@@ -8864,7 +8810,7 @@
     </row>
     <row r="190" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A190" s="10" t="s">
-        <v>480</v>
+        <v>469</v>
       </c>
       <c r="B190" s="11" t="s">
         <v>52</v>
@@ -8888,7 +8834,7 @@
         <v>19</v>
       </c>
       <c r="I190" s="13">
-        <v>873</v>
+        <v>476</v>
       </c>
       <c r="J190" s="14" t="s">
         <v>28</v>
@@ -8896,7 +8842,7 @@
     </row>
     <row r="191" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A191" s="4" t="s">
-        <v>481</v>
+        <v>470</v>
       </c>
       <c r="B191" s="6" t="s">
         <v>59</v>
@@ -8914,13 +8860,13 @@
         <v>63</v>
       </c>
       <c r="G191" s="6" t="s">
-        <v>482</v>
-      </c>
-      <c r="H191" s="16" t="s">
-        <v>129</v>
+        <v>64</v>
+      </c>
+      <c r="H191" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I191" s="8">
-        <v>779</v>
+        <v>260</v>
       </c>
       <c r="J191" s="9" t="s">
         <v>20</v>
@@ -8928,7 +8874,7 @@
     </row>
     <row r="192" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A192" s="10" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="B192" s="12" t="s">
         <v>66</v>
@@ -8952,7 +8898,7 @@
         <v>19</v>
       </c>
       <c r="I192" s="13">
-        <v>717</v>
+        <v>202</v>
       </c>
       <c r="J192" s="15" t="s">
         <v>43</v>
@@ -8960,7 +8906,7 @@
     </row>
     <row r="193" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A193" s="4" t="s">
-        <v>484</v>
+        <v>472</v>
       </c>
       <c r="B193" s="6" t="s">
         <v>73</v>
@@ -8984,7 +8930,7 @@
         <v>19</v>
       </c>
       <c r="I193" s="8">
-        <v>416</v>
+        <v>442</v>
       </c>
       <c r="J193" s="9" t="s">
         <v>20</v>
@@ -8992,22 +8938,22 @@
     </row>
     <row r="194" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A194" s="10" t="s">
-        <v>485</v>
+        <v>473</v>
       </c>
       <c r="B194" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C194" s="12" t="s">
-        <v>486</v>
+        <v>474</v>
       </c>
       <c r="D194" s="12" t="s">
-        <v>487</v>
+        <v>475</v>
       </c>
       <c r="E194" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F194" s="12" t="s">
-        <v>488</v>
+        <v>476</v>
       </c>
       <c r="G194" s="12" t="s">
         <v>85</v>
@@ -9016,7 +8962,7 @@
         <v>19</v>
       </c>
       <c r="I194" s="13">
-        <v>832</v>
+        <v>324</v>
       </c>
       <c r="J194" s="16" t="s">
         <v>86</v>
@@ -9024,7 +8970,7 @@
     </row>
     <row r="195" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A195" s="4" t="s">
-        <v>489</v>
+        <v>477</v>
       </c>
       <c r="B195" s="5" t="s">
         <v>13</v>
@@ -9048,7 +8994,7 @@
         <v>19</v>
       </c>
       <c r="I195" s="8">
-        <v>963</v>
+        <v>632</v>
       </c>
       <c r="J195" s="9" t="s">
         <v>20</v>
@@ -9056,7 +9002,7 @@
     </row>
     <row r="196" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A196" s="10" t="s">
-        <v>490</v>
+        <v>478</v>
       </c>
       <c r="B196" s="11" t="s">
         <v>22</v>
@@ -9080,7 +9026,7 @@
         <v>19</v>
       </c>
       <c r="I196" s="13">
-        <v>835</v>
+        <v>184</v>
       </c>
       <c r="J196" s="15" t="s">
         <v>43</v>
@@ -9088,7 +9034,7 @@
     </row>
     <row r="197" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A197" s="4" t="s">
-        <v>491</v>
+        <v>479</v>
       </c>
       <c r="B197" s="5" t="s">
         <v>30</v>
@@ -9112,7 +9058,7 @@
         <v>19</v>
       </c>
       <c r="I197" s="8">
-        <v>724</v>
+        <v>386</v>
       </c>
       <c r="J197" s="9" t="s">
         <v>20</v>
@@ -9120,7 +9066,7 @@
     </row>
     <row r="198" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A198" s="10" t="s">
-        <v>492</v>
+        <v>480</v>
       </c>
       <c r="B198" s="12" t="s">
         <v>37</v>
@@ -9144,7 +9090,7 @@
         <v>19</v>
       </c>
       <c r="I198" s="13">
-        <v>846</v>
+        <v>777</v>
       </c>
       <c r="J198" s="14" t="s">
         <v>28</v>
@@ -9152,7 +9098,7 @@
     </row>
     <row r="199" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A199" s="4" t="s">
-        <v>493</v>
+        <v>481</v>
       </c>
       <c r="B199" s="5" t="s">
         <v>45</v>
@@ -9176,7 +9122,7 @@
         <v>19</v>
       </c>
       <c r="I199" s="8">
-        <v>889</v>
+        <v>217</v>
       </c>
       <c r="J199" s="9" t="s">
         <v>20</v>
@@ -9184,7 +9130,7 @@
     </row>
     <row r="200" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A200" s="10" t="s">
-        <v>494</v>
+        <v>482</v>
       </c>
       <c r="B200" s="11" t="s">
         <v>52</v>
@@ -9208,7 +9154,7 @@
         <v>19</v>
       </c>
       <c r="I200" s="13">
-        <v>848</v>
+        <v>756</v>
       </c>
       <c r="J200" s="15" t="s">
         <v>43</v>
@@ -9216,7 +9162,7 @@
     </row>
     <row r="201" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A201" s="4" t="s">
-        <v>495</v>
+        <v>483</v>
       </c>
       <c r="B201" s="6" t="s">
         <v>59</v>
@@ -9234,13 +9180,13 @@
         <v>127</v>
       </c>
       <c r="G201" s="6" t="s">
-        <v>216</v>
+        <v>128</v>
       </c>
       <c r="H201" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I201" s="8">
-        <v>504</v>
+        <v>768</v>
       </c>
       <c r="J201" s="9" t="s">
         <v>20</v>
@@ -9248,31 +9194,31 @@
     </row>
     <row r="202" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A202" s="10" t="s">
-        <v>496</v>
+        <v>484</v>
       </c>
       <c r="B202" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C202" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D202" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D202" s="12" t="s">
+      <c r="E202" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E202" s="12" t="s">
+      <c r="F202" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F202" s="12" t="s">
+      <c r="G202" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G202" s="11" t="s">
-        <v>135</v>
-      </c>
       <c r="H202" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I202" s="13">
-        <v>459</v>
+        <v>981</v>
       </c>
       <c r="J202" s="14" t="s">
         <v>28</v>
@@ -9280,31 +9226,31 @@
     </row>
     <row r="203" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A203" s="4" t="s">
-        <v>497</v>
+        <v>485</v>
       </c>
       <c r="B203" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C203" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D203" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D203" s="6" t="s">
+      <c r="E203" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E203" s="6" t="s">
+      <c r="F203" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F203" s="6" t="s">
+      <c r="G203" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G203" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="H203" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I203" s="8">
-        <v>903</v>
+        <v>623</v>
       </c>
       <c r="J203" s="9" t="s">
         <v>20</v>
@@ -9312,31 +9258,31 @@
     </row>
     <row r="204" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A204" s="10" t="s">
-        <v>498</v>
+        <v>486</v>
       </c>
       <c r="B204" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C204" s="12" t="s">
-        <v>499</v>
+        <v>487</v>
       </c>
       <c r="D204" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E204" s="12" t="s">
-        <v>500</v>
+        <v>488</v>
       </c>
       <c r="F204" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G204" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G204" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H204" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I204" s="13">
-        <v>335</v>
+        <v>194</v>
       </c>
       <c r="J204" s="16" t="s">
         <v>86</v>
@@ -9344,31 +9290,31 @@
     </row>
     <row r="205" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A205" s="4" t="s">
-        <v>501</v>
+        <v>489</v>
       </c>
       <c r="B205" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C205" s="6" t="s">
-        <v>502</v>
+        <v>490</v>
       </c>
       <c r="D205" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E205" s="6" t="s">
-        <v>503</v>
+        <v>491</v>
       </c>
       <c r="F205" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G205" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G205" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H205" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I205" s="8">
-        <v>816</v>
+        <v>756</v>
       </c>
       <c r="J205" s="9" t="s">
         <v>20</v>
@@ -9376,31 +9322,31 @@
     </row>
     <row r="206" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A206" s="10" t="s">
-        <v>504</v>
+        <v>492</v>
       </c>
       <c r="B206" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C206" s="12" t="s">
-        <v>505</v>
+        <v>493</v>
       </c>
       <c r="D206" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E206" s="12" t="s">
-        <v>506</v>
+        <v>494</v>
       </c>
       <c r="F206" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G206" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G206" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H206" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I206" s="13">
-        <v>591</v>
+        <v>889</v>
       </c>
       <c r="J206" s="14" t="s">
         <v>28</v>
@@ -9408,31 +9354,31 @@
     </row>
     <row r="207" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A207" s="4" t="s">
-        <v>507</v>
+        <v>495</v>
       </c>
       <c r="B207" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C207" s="6" t="s">
-        <v>508</v>
+        <v>496</v>
       </c>
       <c r="D207" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E207" s="6" t="s">
-        <v>509</v>
+        <v>497</v>
       </c>
       <c r="F207" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G207" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G207" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H207" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I207" s="8">
-        <v>519</v>
+        <v>959</v>
       </c>
       <c r="J207" s="9" t="s">
         <v>20</v>
@@ -9440,31 +9386,31 @@
     </row>
     <row r="208" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A208" s="10" t="s">
-        <v>510</v>
+        <v>498</v>
       </c>
       <c r="B208" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C208" s="12" t="s">
-        <v>511</v>
+        <v>499</v>
       </c>
       <c r="D208" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E208" s="12" t="s">
-        <v>512</v>
+        <v>500</v>
       </c>
       <c r="F208" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G208" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G208" s="11" t="s">
-        <v>513</v>
-      </c>
-      <c r="H208" s="16" t="s">
-        <v>129</v>
+      <c r="H208" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I208" s="13">
-        <v>599</v>
+        <v>485</v>
       </c>
       <c r="J208" s="15" t="s">
         <v>43</v>
@@ -9472,31 +9418,31 @@
     </row>
     <row r="209" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A209" s="4" t="s">
-        <v>514</v>
+        <v>501</v>
       </c>
       <c r="B209" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C209" s="6" t="s">
-        <v>515</v>
+        <v>502</v>
       </c>
       <c r="D209" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E209" s="6" t="s">
-        <v>516</v>
+        <v>503</v>
       </c>
       <c r="F209" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G209" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G209" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H209" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I209" s="8">
-        <v>588</v>
+        <v>934</v>
       </c>
       <c r="J209" s="9" t="s">
         <v>20</v>
@@ -9504,31 +9450,31 @@
     </row>
     <row r="210" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A210" s="10" t="s">
-        <v>517</v>
+        <v>504</v>
       </c>
       <c r="B210" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C210" s="12" t="s">
-        <v>518</v>
+        <v>505</v>
       </c>
       <c r="D210" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E210" s="12" t="s">
-        <v>519</v>
+        <v>506</v>
       </c>
       <c r="F210" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G210" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G210" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H210" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I210" s="13">
-        <v>385</v>
+        <v>621</v>
       </c>
       <c r="J210" s="14" t="s">
         <v>28</v>
@@ -9536,31 +9482,31 @@
     </row>
     <row r="211" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A211" s="4" t="s">
-        <v>520</v>
+        <v>507</v>
       </c>
       <c r="B211" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C211" s="6" t="s">
-        <v>521</v>
+        <v>508</v>
       </c>
       <c r="D211" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E211" s="6" t="s">
-        <v>522</v>
+        <v>509</v>
       </c>
       <c r="F211" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G211" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G211" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H211" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I211" s="8">
-        <v>306</v>
+        <v>966</v>
       </c>
       <c r="J211" s="9" t="s">
         <v>20</v>
@@ -9568,31 +9514,31 @@
     </row>
     <row r="212" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A212" s="10" t="s">
-        <v>523</v>
+        <v>510</v>
       </c>
       <c r="B212" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C212" s="12" t="s">
-        <v>524</v>
+        <v>511</v>
       </c>
       <c r="D212" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E212" s="12" t="s">
-        <v>525</v>
+        <v>512</v>
       </c>
       <c r="F212" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G212" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G212" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H212" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I212" s="13">
-        <v>888</v>
+        <v>419</v>
       </c>
       <c r="J212" s="15" t="s">
         <v>43</v>
@@ -9600,31 +9546,31 @@
     </row>
     <row r="213" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A213" s="4" t="s">
-        <v>526</v>
+        <v>513</v>
       </c>
       <c r="B213" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C213" s="6" t="s">
-        <v>527</v>
+        <v>514</v>
       </c>
       <c r="D213" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E213" s="6" t="s">
-        <v>528</v>
+        <v>515</v>
       </c>
       <c r="F213" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G213" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G213" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H213" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I213" s="8">
-        <v>364</v>
+        <v>676</v>
       </c>
       <c r="J213" s="9" t="s">
         <v>20</v>
@@ -9632,31 +9578,31 @@
     </row>
     <row r="214" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A214" s="10" t="s">
-        <v>529</v>
+        <v>516</v>
       </c>
       <c r="B214" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C214" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D214" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="D214" s="12" t="s">
+      <c r="E214" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E214" s="12" t="s">
+      <c r="F214" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="F214" s="12" t="s">
+      <c r="G214" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="G214" s="12" t="s">
-        <v>189</v>
-      </c>
       <c r="H214" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I214" s="13">
-        <v>989</v>
+        <v>549</v>
       </c>
       <c r="J214" s="16" t="s">
         <v>86</v>
@@ -9664,7 +9610,7 @@
     </row>
     <row r="215" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A215" s="4" t="s">
-        <v>530</v>
+        <v>517</v>
       </c>
       <c r="B215" s="5" t="s">
         <v>13</v>
@@ -9688,7 +9634,7 @@
         <v>19</v>
       </c>
       <c r="I215" s="8">
-        <v>262</v>
+        <v>977</v>
       </c>
       <c r="J215" s="9" t="s">
         <v>20</v>
@@ -9696,7 +9642,7 @@
     </row>
     <row r="216" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A216" s="10" t="s">
-        <v>531</v>
+        <v>518</v>
       </c>
       <c r="B216" s="11" t="s">
         <v>22</v>
@@ -9720,7 +9666,7 @@
         <v>19</v>
       </c>
       <c r="I216" s="13">
-        <v>588</v>
+        <v>769</v>
       </c>
       <c r="J216" s="15" t="s">
         <v>43</v>
@@ -9728,7 +9674,7 @@
     </row>
     <row r="217" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A217" s="4" t="s">
-        <v>532</v>
+        <v>519</v>
       </c>
       <c r="B217" s="5" t="s">
         <v>30</v>
@@ -9752,7 +9698,7 @@
         <v>19</v>
       </c>
       <c r="I217" s="8">
-        <v>285</v>
+        <v>444</v>
       </c>
       <c r="J217" s="9" t="s">
         <v>20</v>
@@ -9760,22 +9706,22 @@
     </row>
     <row r="218" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A218" s="10" t="s">
-        <v>533</v>
+        <v>520</v>
       </c>
       <c r="B218" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C218" s="12" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D218" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E218" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="F218" s="12" t="s">
         <v>195</v>
-      </c>
-      <c r="F218" s="12" t="s">
-        <v>196</v>
       </c>
       <c r="G218" s="12" t="s">
         <v>42</v>
@@ -9784,7 +9730,7 @@
         <v>19</v>
       </c>
       <c r="I218" s="13">
-        <v>234</v>
+        <v>324</v>
       </c>
       <c r="J218" s="14" t="s">
         <v>28</v>
@@ -9792,7 +9738,7 @@
     </row>
     <row r="219" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A219" s="4" t="s">
-        <v>534</v>
+        <v>521</v>
       </c>
       <c r="B219" s="5" t="s">
         <v>45</v>
@@ -9816,7 +9762,7 @@
         <v>19</v>
       </c>
       <c r="I219" s="8">
-        <v>276</v>
+        <v>372</v>
       </c>
       <c r="J219" s="9" t="s">
         <v>20</v>
@@ -9824,7 +9770,7 @@
     </row>
     <row r="220" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A220" s="10" t="s">
-        <v>535</v>
+        <v>522</v>
       </c>
       <c r="B220" s="11" t="s">
         <v>52</v>
@@ -9848,7 +9794,7 @@
         <v>19</v>
       </c>
       <c r="I220" s="13">
-        <v>788</v>
+        <v>987</v>
       </c>
       <c r="J220" s="15" t="s">
         <v>43</v>
@@ -9856,7 +9802,7 @@
     </row>
     <row r="221" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A221" s="4" t="s">
-        <v>536</v>
+        <v>523</v>
       </c>
       <c r="B221" s="6" t="s">
         <v>59</v>
@@ -9880,7 +9826,7 @@
         <v>19</v>
       </c>
       <c r="I221" s="8">
-        <v>913</v>
+        <v>412</v>
       </c>
       <c r="J221" s="9" t="s">
         <v>20</v>
@@ -9888,7 +9834,7 @@
     </row>
     <row r="222" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A222" s="10" t="s">
-        <v>537</v>
+        <v>524</v>
       </c>
       <c r="B222" s="12" t="s">
         <v>66</v>
@@ -9912,7 +9858,7 @@
         <v>19</v>
       </c>
       <c r="I222" s="13">
-        <v>453</v>
+        <v>243</v>
       </c>
       <c r="J222" s="14" t="s">
         <v>28</v>
@@ -9920,7 +9866,7 @@
     </row>
     <row r="223" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A223" s="4" t="s">
-        <v>538</v>
+        <v>525</v>
       </c>
       <c r="B223" s="6" t="s">
         <v>73</v>
@@ -9944,7 +9890,7 @@
         <v>19</v>
       </c>
       <c r="I223" s="8">
-        <v>812</v>
+        <v>479</v>
       </c>
       <c r="J223" s="9" t="s">
         <v>20</v>
@@ -9952,22 +9898,22 @@
     </row>
     <row r="224" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A224" s="10" t="s">
-        <v>539</v>
+        <v>526</v>
       </c>
       <c r="B224" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C224" s="12" t="s">
-        <v>540</v>
+        <v>527</v>
       </c>
       <c r="D224" s="12" t="s">
-        <v>541</v>
+        <v>528</v>
       </c>
       <c r="E224" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F224" s="12" t="s">
-        <v>542</v>
+        <v>529</v>
       </c>
       <c r="G224" s="12" t="s">
         <v>85</v>
@@ -9976,7 +9922,7 @@
         <v>19</v>
       </c>
       <c r="I224" s="13">
-        <v>597</v>
+        <v>330</v>
       </c>
       <c r="J224" s="16" t="s">
         <v>86</v>
@@ -9984,13 +9930,13 @@
     </row>
     <row r="225" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A225" s="4" t="s">
-        <v>543</v>
+        <v>530</v>
       </c>
       <c r="B225" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C225" s="6" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="D225" s="6" t="s">
         <v>89</v>
@@ -9999,16 +9945,16 @@
         <v>90</v>
       </c>
       <c r="F225" s="6" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="G225" s="6" t="s">
-        <v>544</v>
-      </c>
-      <c r="H225" s="16" t="s">
-        <v>129</v>
+        <v>92</v>
+      </c>
+      <c r="H225" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I225" s="8">
-        <v>381</v>
+        <v>518</v>
       </c>
       <c r="J225" s="9" t="s">
         <v>20</v>
@@ -10016,7 +9962,7 @@
     </row>
     <row r="226" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A226" s="10" t="s">
-        <v>545</v>
+        <v>531</v>
       </c>
       <c r="B226" s="11" t="s">
         <v>22</v>
@@ -10040,7 +9986,7 @@
         <v>19</v>
       </c>
       <c r="I226" s="13">
-        <v>410</v>
+        <v>847</v>
       </c>
       <c r="J226" s="14" t="s">
         <v>28</v>
@@ -10048,7 +9994,7 @@
     </row>
     <row r="227" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A227" s="4" t="s">
-        <v>546</v>
+        <v>532</v>
       </c>
       <c r="B227" s="5" t="s">
         <v>30</v>
@@ -10072,7 +10018,7 @@
         <v>19</v>
       </c>
       <c r="I227" s="8">
-        <v>665</v>
+        <v>445</v>
       </c>
       <c r="J227" s="9" t="s">
         <v>20</v>
@@ -10080,7 +10026,7 @@
     </row>
     <row r="228" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A228" s="10" t="s">
-        <v>547</v>
+        <v>533</v>
       </c>
       <c r="B228" s="12" t="s">
         <v>37</v>
@@ -10104,7 +10050,7 @@
         <v>19</v>
       </c>
       <c r="I228" s="13">
-        <v>620</v>
+        <v>300</v>
       </c>
       <c r="J228" s="15" t="s">
         <v>43</v>
@@ -10112,7 +10058,7 @@
     </row>
     <row r="229" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A229" s="4" t="s">
-        <v>548</v>
+        <v>534</v>
       </c>
       <c r="B229" s="5" t="s">
         <v>45</v>
@@ -10136,7 +10082,7 @@
         <v>19</v>
       </c>
       <c r="I229" s="8">
-        <v>336</v>
+        <v>912</v>
       </c>
       <c r="J229" s="9" t="s">
         <v>20</v>
@@ -10144,7 +10090,7 @@
     </row>
     <row r="230" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A230" s="10" t="s">
-        <v>549</v>
+        <v>535</v>
       </c>
       <c r="B230" s="11" t="s">
         <v>52</v>
@@ -10168,7 +10114,7 @@
         <v>19</v>
       </c>
       <c r="I230" s="13">
-        <v>707</v>
+        <v>369</v>
       </c>
       <c r="J230" s="14" t="s">
         <v>28</v>
@@ -10176,7 +10122,7 @@
     </row>
     <row r="231" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A231" s="4" t="s">
-        <v>550</v>
+        <v>536</v>
       </c>
       <c r="B231" s="6" t="s">
         <v>59</v>
@@ -10194,13 +10140,13 @@
         <v>127</v>
       </c>
       <c r="G231" s="6" t="s">
-        <v>216</v>
+        <v>128</v>
       </c>
       <c r="H231" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I231" s="8">
-        <v>422</v>
+        <v>373</v>
       </c>
       <c r="J231" s="9" t="s">
         <v>20</v>
@@ -10208,31 +10154,31 @@
     </row>
     <row r="232" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A232" s="10" t="s">
-        <v>551</v>
+        <v>537</v>
       </c>
       <c r="B232" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C232" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D232" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D232" s="12" t="s">
+      <c r="E232" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E232" s="12" t="s">
+      <c r="F232" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F232" s="12" t="s">
+      <c r="G232" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G232" s="11" t="s">
-        <v>135</v>
-      </c>
       <c r="H232" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I232" s="13">
-        <v>337</v>
+        <v>644</v>
       </c>
       <c r="J232" s="15" t="s">
         <v>43</v>
@@ -10240,31 +10186,31 @@
     </row>
     <row r="233" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A233" s="4" t="s">
-        <v>552</v>
+        <v>538</v>
       </c>
       <c r="B233" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C233" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D233" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D233" s="6" t="s">
+      <c r="E233" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E233" s="6" t="s">
+      <c r="F233" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F233" s="6" t="s">
+      <c r="G233" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G233" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="H233" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I233" s="8">
-        <v>651</v>
+        <v>202</v>
       </c>
       <c r="J233" s="9" t="s">
         <v>20</v>
@@ -10272,31 +10218,31 @@
     </row>
     <row r="234" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A234" s="10" t="s">
-        <v>553</v>
+        <v>539</v>
       </c>
       <c r="B234" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C234" s="12" t="s">
-        <v>554</v>
+        <v>540</v>
       </c>
       <c r="D234" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E234" s="12" t="s">
-        <v>555</v>
+        <v>541</v>
       </c>
       <c r="F234" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G234" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G234" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H234" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I234" s="13">
-        <v>482</v>
+        <v>980</v>
       </c>
       <c r="J234" s="16" t="s">
         <v>86</v>
@@ -10304,31 +10250,31 @@
     </row>
     <row r="235" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A235" s="4" t="s">
-        <v>556</v>
+        <v>542</v>
       </c>
       <c r="B235" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C235" s="6" t="s">
-        <v>557</v>
+        <v>543</v>
       </c>
       <c r="D235" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E235" s="6" t="s">
-        <v>558</v>
+        <v>544</v>
       </c>
       <c r="F235" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G235" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G235" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H235" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I235" s="8">
-        <v>465</v>
+        <v>716</v>
       </c>
       <c r="J235" s="9" t="s">
         <v>20</v>
@@ -10336,31 +10282,31 @@
     </row>
     <row r="236" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A236" s="10" t="s">
-        <v>559</v>
+        <v>545</v>
       </c>
       <c r="B236" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C236" s="12" t="s">
-        <v>560</v>
+        <v>546</v>
       </c>
       <c r="D236" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E236" s="12" t="s">
-        <v>561</v>
+        <v>547</v>
       </c>
       <c r="F236" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G236" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G236" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H236" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I236" s="13">
-        <v>257</v>
+        <v>352</v>
       </c>
       <c r="J236" s="15" t="s">
         <v>43</v>
@@ -10368,31 +10314,31 @@
     </row>
     <row r="237" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A237" s="4" t="s">
-        <v>562</v>
+        <v>548</v>
       </c>
       <c r="B237" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C237" s="6" t="s">
-        <v>563</v>
+        <v>549</v>
       </c>
       <c r="D237" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E237" s="6" t="s">
-        <v>564</v>
+        <v>550</v>
       </c>
       <c r="F237" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G237" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G237" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H237" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I237" s="8">
-        <v>683</v>
+        <v>805</v>
       </c>
       <c r="J237" s="9" t="s">
         <v>20</v>
@@ -10400,31 +10346,31 @@
     </row>
     <row r="238" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A238" s="10" t="s">
-        <v>565</v>
+        <v>551</v>
       </c>
       <c r="B238" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C238" s="12" t="s">
-        <v>566</v>
+        <v>552</v>
       </c>
       <c r="D238" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E238" s="12" t="s">
-        <v>567</v>
+        <v>553</v>
       </c>
       <c r="F238" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G238" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G238" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H238" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I238" s="13">
-        <v>460</v>
+        <v>229</v>
       </c>
       <c r="J238" s="14" t="s">
         <v>28</v>
@@ -10432,31 +10378,31 @@
     </row>
     <row r="239" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A239" s="4" t="s">
-        <v>568</v>
+        <v>554</v>
       </c>
       <c r="B239" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C239" s="6" t="s">
-        <v>569</v>
+        <v>555</v>
       </c>
       <c r="D239" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E239" s="6" t="s">
-        <v>570</v>
+        <v>556</v>
       </c>
       <c r="F239" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G239" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G239" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H239" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I239" s="8">
-        <v>570</v>
+        <v>411</v>
       </c>
       <c r="J239" s="9" t="s">
         <v>20</v>
@@ -10464,31 +10410,31 @@
     </row>
     <row r="240" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A240" s="10" t="s">
-        <v>571</v>
+        <v>557</v>
       </c>
       <c r="B240" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C240" s="12" t="s">
-        <v>572</v>
+        <v>558</v>
       </c>
       <c r="D240" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E240" s="12" t="s">
-        <v>573</v>
+        <v>559</v>
       </c>
       <c r="F240" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G240" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G240" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H240" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I240" s="13">
-        <v>464</v>
+        <v>887</v>
       </c>
       <c r="J240" s="15" t="s">
         <v>43</v>
@@ -10496,31 +10442,31 @@
     </row>
     <row r="241" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A241" s="4" t="s">
-        <v>574</v>
+        <v>560</v>
       </c>
       <c r="B241" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C241" s="6" t="s">
-        <v>575</v>
+        <v>561</v>
       </c>
       <c r="D241" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E241" s="6" t="s">
-        <v>576</v>
+        <v>562</v>
       </c>
       <c r="F241" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G241" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G241" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H241" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I241" s="8">
-        <v>360</v>
+        <v>745</v>
       </c>
       <c r="J241" s="9" t="s">
         <v>20</v>
@@ -10528,31 +10474,31 @@
     </row>
     <row r="242" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A242" s="10" t="s">
-        <v>577</v>
+        <v>563</v>
       </c>
       <c r="B242" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C242" s="12" t="s">
-        <v>578</v>
+        <v>564</v>
       </c>
       <c r="D242" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E242" s="12" t="s">
-        <v>579</v>
+        <v>565</v>
       </c>
       <c r="F242" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G242" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G242" s="11" t="s">
-        <v>580</v>
-      </c>
-      <c r="H242" s="16" t="s">
-        <v>129</v>
+      <c r="H242" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I242" s="13">
-        <v>600</v>
+        <v>447</v>
       </c>
       <c r="J242" s="14" t="s">
         <v>28</v>
@@ -10560,31 +10506,31 @@
     </row>
     <row r="243" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A243" s="4" t="s">
-        <v>581</v>
+        <v>566</v>
       </c>
       <c r="B243" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C243" s="6" t="s">
-        <v>582</v>
+        <v>567</v>
       </c>
       <c r="D243" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E243" s="6" t="s">
-        <v>583</v>
+        <v>568</v>
       </c>
       <c r="F243" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G243" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G243" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H243" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I243" s="8">
-        <v>911</v>
+        <v>564</v>
       </c>
       <c r="J243" s="9" t="s">
         <v>20</v>
@@ -10592,31 +10538,31 @@
     </row>
     <row r="244" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A244" s="10" t="s">
-        <v>584</v>
+        <v>569</v>
       </c>
       <c r="B244" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C244" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D244" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="D244" s="12" t="s">
+      <c r="E244" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E244" s="12" t="s">
+      <c r="F244" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="F244" s="12" t="s">
+      <c r="G244" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="G244" s="12" t="s">
-        <v>189</v>
-      </c>
       <c r="H244" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I244" s="13">
-        <v>600</v>
+        <v>718</v>
       </c>
       <c r="J244" s="16" t="s">
         <v>86</v>
@@ -10624,7 +10570,7 @@
     </row>
     <row r="245" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A245" s="4" t="s">
-        <v>585</v>
+        <v>570</v>
       </c>
       <c r="B245" s="5" t="s">
         <v>13</v>
@@ -10648,7 +10594,7 @@
         <v>19</v>
       </c>
       <c r="I245" s="8">
-        <v>983</v>
+        <v>290</v>
       </c>
       <c r="J245" s="9" t="s">
         <v>20</v>
@@ -10656,7 +10602,7 @@
     </row>
     <row r="246" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A246" s="10" t="s">
-        <v>586</v>
+        <v>571</v>
       </c>
       <c r="B246" s="11" t="s">
         <v>22</v>
@@ -10680,7 +10626,7 @@
         <v>19</v>
       </c>
       <c r="I246" s="13">
-        <v>564</v>
+        <v>562</v>
       </c>
       <c r="J246" s="14" t="s">
         <v>28</v>
@@ -10688,7 +10634,7 @@
     </row>
     <row r="247" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A247" s="4" t="s">
-        <v>587</v>
+        <v>572</v>
       </c>
       <c r="B247" s="5" t="s">
         <v>30</v>
@@ -10712,7 +10658,7 @@
         <v>19</v>
       </c>
       <c r="I247" s="8">
-        <v>392</v>
+        <v>876</v>
       </c>
       <c r="J247" s="9" t="s">
         <v>20</v>
@@ -10720,22 +10666,22 @@
     </row>
     <row r="248" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A248" s="10" t="s">
-        <v>588</v>
+        <v>573</v>
       </c>
       <c r="B248" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C248" s="12" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D248" s="12" t="s">
         <v>39</v>
       </c>
       <c r="E248" s="12" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F248" s="12" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="G248" s="12" t="s">
         <v>42</v>
@@ -10744,7 +10690,7 @@
         <v>19</v>
       </c>
       <c r="I248" s="13">
-        <v>312</v>
+        <v>679</v>
       </c>
       <c r="J248" s="15" t="s">
         <v>43</v>
@@ -10752,7 +10698,7 @@
     </row>
     <row r="249" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A249" s="4" t="s">
-        <v>589</v>
+        <v>574</v>
       </c>
       <c r="B249" s="5" t="s">
         <v>45</v>
@@ -10776,7 +10722,7 @@
         <v>19</v>
       </c>
       <c r="I249" s="8">
-        <v>913</v>
+        <v>595</v>
       </c>
       <c r="J249" s="9" t="s">
         <v>20</v>
@@ -10784,7 +10730,7 @@
     </row>
     <row r="250" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A250" s="10" t="s">
-        <v>590</v>
+        <v>575</v>
       </c>
       <c r="B250" s="11" t="s">
         <v>52</v>
@@ -10808,7 +10754,7 @@
         <v>19</v>
       </c>
       <c r="I250" s="13">
-        <v>182</v>
+        <v>654</v>
       </c>
       <c r="J250" s="14" t="s">
         <v>28</v>
@@ -10816,7 +10762,7 @@
     </row>
     <row r="251" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A251" s="4" t="s">
-        <v>591</v>
+        <v>576</v>
       </c>
       <c r="B251" s="6" t="s">
         <v>59</v>
@@ -10840,7 +10786,7 @@
         <v>19</v>
       </c>
       <c r="I251" s="8">
-        <v>741</v>
+        <v>387</v>
       </c>
       <c r="J251" s="9" t="s">
         <v>20</v>
@@ -10848,7 +10794,7 @@
     </row>
     <row r="252" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A252" s="10" t="s">
-        <v>592</v>
+        <v>577</v>
       </c>
       <c r="B252" s="12" t="s">
         <v>66</v>
@@ -10872,7 +10818,7 @@
         <v>19</v>
       </c>
       <c r="I252" s="13">
-        <v>435</v>
+        <v>890</v>
       </c>
       <c r="J252" s="15" t="s">
         <v>43</v>
@@ -10880,7 +10826,7 @@
     </row>
     <row r="253" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A253" s="4" t="s">
-        <v>593</v>
+        <v>578</v>
       </c>
       <c r="B253" s="6" t="s">
         <v>73</v>
@@ -10904,7 +10850,7 @@
         <v>19</v>
       </c>
       <c r="I253" s="8">
-        <v>963</v>
+        <v>265</v>
       </c>
       <c r="J253" s="9" t="s">
         <v>20</v>
@@ -10912,22 +10858,22 @@
     </row>
     <row r="254" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A254" s="10" t="s">
-        <v>594</v>
+        <v>579</v>
       </c>
       <c r="B254" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C254" s="12" t="s">
-        <v>595</v>
+        <v>580</v>
       </c>
       <c r="D254" s="12" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
       <c r="E254" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F254" s="12" t="s">
-        <v>597</v>
+        <v>582</v>
       </c>
       <c r="G254" s="12" t="s">
         <v>85</v>
@@ -10936,7 +10882,7 @@
         <v>19</v>
       </c>
       <c r="I254" s="13">
-        <v>724</v>
+        <v>400</v>
       </c>
       <c r="J254" s="16" t="s">
         <v>86</v>
@@ -10944,13 +10890,13 @@
     </row>
     <row r="255" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A255" s="4" t="s">
-        <v>598</v>
+        <v>583</v>
       </c>
       <c r="B255" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C255" s="6" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D255" s="6" t="s">
         <v>89</v>
@@ -10959,7 +10905,7 @@
         <v>90</v>
       </c>
       <c r="F255" s="6" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="G255" s="6" t="s">
         <v>92</v>
@@ -10968,7 +10914,7 @@
         <v>19</v>
       </c>
       <c r="I255" s="8">
-        <v>682</v>
+        <v>655</v>
       </c>
       <c r="J255" s="9" t="s">
         <v>20</v>
@@ -10976,7 +10922,7 @@
     </row>
     <row r="256" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A256" s="10" t="s">
-        <v>599</v>
+        <v>584</v>
       </c>
       <c r="B256" s="11" t="s">
         <v>22</v>
@@ -11000,7 +10946,7 @@
         <v>19</v>
       </c>
       <c r="I256" s="13">
-        <v>981</v>
+        <v>371</v>
       </c>
       <c r="J256" s="15" t="s">
         <v>43</v>
@@ -11008,7 +10954,7 @@
     </row>
     <row r="257" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A257" s="4" t="s">
-        <v>600</v>
+        <v>585</v>
       </c>
       <c r="B257" s="5" t="s">
         <v>30</v>
@@ -11032,7 +10978,7 @@
         <v>19</v>
       </c>
       <c r="I257" s="8">
-        <v>279</v>
+        <v>331</v>
       </c>
       <c r="J257" s="9" t="s">
         <v>20</v>
@@ -11040,7 +10986,7 @@
     </row>
     <row r="258" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A258" s="10" t="s">
-        <v>601</v>
+        <v>586</v>
       </c>
       <c r="B258" s="12" t="s">
         <v>37</v>
@@ -11064,7 +11010,7 @@
         <v>19</v>
       </c>
       <c r="I258" s="13">
-        <v>357</v>
+        <v>687</v>
       </c>
       <c r="J258" s="14" t="s">
         <v>28</v>
@@ -11072,7 +11018,7 @@
     </row>
     <row r="259" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A259" s="4" t="s">
-        <v>602</v>
+        <v>587</v>
       </c>
       <c r="B259" s="5" t="s">
         <v>45</v>
@@ -11090,13 +11036,13 @@
         <v>115</v>
       </c>
       <c r="G259" s="6" t="s">
-        <v>603</v>
-      </c>
-      <c r="H259" s="16" t="s">
-        <v>129</v>
+        <v>116</v>
+      </c>
+      <c r="H259" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I259" s="8">
-        <v>380</v>
+        <v>910</v>
       </c>
       <c r="J259" s="9" t="s">
         <v>20</v>
@@ -11104,7 +11050,7 @@
     </row>
     <row r="260" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A260" s="10" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="B260" s="11" t="s">
         <v>52</v>
@@ -11128,7 +11074,7 @@
         <v>19</v>
       </c>
       <c r="I260" s="13">
-        <v>510</v>
+        <v>475</v>
       </c>
       <c r="J260" s="15" t="s">
         <v>43</v>
@@ -11136,7 +11082,7 @@
     </row>
     <row r="261" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A261" s="4" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="B261" s="6" t="s">
         <v>59</v>
@@ -11154,13 +11100,13 @@
         <v>127</v>
       </c>
       <c r="G261" s="6" t="s">
-        <v>216</v>
+        <v>128</v>
       </c>
       <c r="H261" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I261" s="8">
-        <v>836</v>
+        <v>639</v>
       </c>
       <c r="J261" s="9" t="s">
         <v>20</v>
@@ -11168,31 +11114,31 @@
     </row>
     <row r="262" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A262" s="10" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="B262" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C262" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D262" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D262" s="12" t="s">
+      <c r="E262" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E262" s="12" t="s">
+      <c r="F262" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F262" s="12" t="s">
+      <c r="G262" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G262" s="11" t="s">
-        <v>135</v>
-      </c>
       <c r="H262" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I262" s="13">
-        <v>523</v>
+        <v>443</v>
       </c>
       <c r="J262" s="14" t="s">
         <v>28</v>
@@ -11200,31 +11146,31 @@
     </row>
     <row r="263" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A263" s="4" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="B263" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C263" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D263" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D263" s="6" t="s">
+      <c r="E263" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E263" s="6" t="s">
+      <c r="F263" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F263" s="6" t="s">
+      <c r="G263" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G263" s="6" t="s">
-        <v>141</v>
-      </c>
       <c r="H263" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I263" s="8">
-        <v>272</v>
+        <v>455</v>
       </c>
       <c r="J263" s="9" t="s">
         <v>20</v>
@@ -11232,31 +11178,31 @@
     </row>
     <row r="264" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A264" s="10" t="s">
-        <v>608</v>
+        <v>592</v>
       </c>
       <c r="B264" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C264" s="12" t="s">
-        <v>609</v>
+        <v>593</v>
       </c>
       <c r="D264" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E264" s="12" t="s">
-        <v>610</v>
+        <v>594</v>
       </c>
       <c r="F264" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G264" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G264" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H264" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I264" s="13">
-        <v>401</v>
+        <v>912</v>
       </c>
       <c r="J264" s="16" t="s">
         <v>86</v>
@@ -11264,31 +11210,31 @@
     </row>
     <row r="265" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A265" s="4" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="B265" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C265" s="6" t="s">
-        <v>612</v>
+        <v>596</v>
       </c>
       <c r="D265" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E265" s="6" t="s">
-        <v>613</v>
+        <v>597</v>
       </c>
       <c r="F265" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G265" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G265" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H265" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I265" s="8">
-        <v>663</v>
+        <v>905</v>
       </c>
       <c r="J265" s="9" t="s">
         <v>20</v>
@@ -11296,31 +11242,31 @@
     </row>
     <row r="266" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A266" s="10" t="s">
-        <v>614</v>
+        <v>598</v>
       </c>
       <c r="B266" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C266" s="12" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="D266" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E266" s="12" t="s">
-        <v>616</v>
+        <v>600</v>
       </c>
       <c r="F266" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G266" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G266" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H266" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I266" s="13">
-        <v>850</v>
+        <v>986</v>
       </c>
       <c r="J266" s="14" t="s">
         <v>28</v>
@@ -11328,31 +11274,31 @@
     </row>
     <row r="267" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A267" s="4" t="s">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="B267" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C267" s="6" t="s">
-        <v>618</v>
+        <v>602</v>
       </c>
       <c r="D267" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E267" s="6" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="F267" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G267" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G267" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H267" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I267" s="8">
-        <v>473</v>
+        <v>439</v>
       </c>
       <c r="J267" s="9" t="s">
         <v>20</v>
@@ -11360,31 +11306,31 @@
     </row>
     <row r="268" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A268" s="10" t="s">
-        <v>620</v>
+        <v>604</v>
       </c>
       <c r="B268" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C268" s="12" t="s">
-        <v>621</v>
+        <v>605</v>
       </c>
       <c r="D268" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E268" s="12" t="s">
-        <v>622</v>
+        <v>606</v>
       </c>
       <c r="F268" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G268" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G268" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H268" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I268" s="13">
-        <v>376</v>
+        <v>774</v>
       </c>
       <c r="J268" s="15" t="s">
         <v>43</v>
@@ -11392,31 +11338,31 @@
     </row>
     <row r="269" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A269" s="4" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="B269" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C269" s="6" t="s">
-        <v>624</v>
+        <v>608</v>
       </c>
       <c r="D269" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E269" s="6" t="s">
-        <v>625</v>
+        <v>609</v>
       </c>
       <c r="F269" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G269" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G269" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H269" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I269" s="8">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="J269" s="9" t="s">
         <v>20</v>
@@ -11424,31 +11370,31 @@
     </row>
     <row r="270" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A270" s="10" t="s">
-        <v>626</v>
+        <v>610</v>
       </c>
       <c r="B270" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C270" s="12" t="s">
-        <v>627</v>
+        <v>611</v>
       </c>
       <c r="D270" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E270" s="12" t="s">
-        <v>628</v>
+        <v>612</v>
       </c>
       <c r="F270" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G270" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G270" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H270" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I270" s="13">
-        <v>826</v>
+        <v>777</v>
       </c>
       <c r="J270" s="14" t="s">
         <v>28</v>
@@ -11456,31 +11402,31 @@
     </row>
     <row r="271" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A271" s="4" t="s">
-        <v>629</v>
+        <v>613</v>
       </c>
       <c r="B271" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C271" s="6" t="s">
-        <v>630</v>
+        <v>614</v>
       </c>
       <c r="D271" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E271" s="6" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="F271" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G271" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G271" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H271" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I271" s="8">
-        <v>732</v>
+        <v>191</v>
       </c>
       <c r="J271" s="9" t="s">
         <v>20</v>
@@ -11488,31 +11434,31 @@
     </row>
     <row r="272" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A272" s="10" t="s">
-        <v>632</v>
+        <v>616</v>
       </c>
       <c r="B272" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C272" s="12" t="s">
-        <v>633</v>
+        <v>617</v>
       </c>
       <c r="D272" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E272" s="12" t="s">
-        <v>634</v>
+        <v>618</v>
       </c>
       <c r="F272" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G272" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G272" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H272" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I272" s="13">
-        <v>751</v>
+        <v>985</v>
       </c>
       <c r="J272" s="15" t="s">
         <v>43</v>
@@ -11520,31 +11466,31 @@
     </row>
     <row r="273" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A273" s="4" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="B273" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C273" s="6" t="s">
-        <v>636</v>
+        <v>620</v>
       </c>
       <c r="D273" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E273" s="6" t="s">
-        <v>637</v>
+        <v>621</v>
       </c>
       <c r="F273" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G273" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G273" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H273" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I273" s="8">
-        <v>602</v>
+        <v>791</v>
       </c>
       <c r="J273" s="9" t="s">
         <v>20</v>
@@ -11552,31 +11498,31 @@
     </row>
     <row r="274" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A274" s="10" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="B274" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C274" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D274" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="D274" s="12" t="s">
+      <c r="E274" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E274" s="12" t="s">
+      <c r="F274" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="F274" s="12" t="s">
+      <c r="G274" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="G274" s="12" t="s">
-        <v>189</v>
-      </c>
       <c r="H274" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I274" s="13">
-        <v>510</v>
+        <v>357</v>
       </c>
       <c r="J274" s="16" t="s">
         <v>86</v>
@@ -11584,7 +11530,7 @@
     </row>
     <row r="275" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A275" s="4" t="s">
-        <v>639</v>
+        <v>623</v>
       </c>
       <c r="B275" s="5" t="s">
         <v>13</v>
@@ -11608,7 +11554,7 @@
         <v>19</v>
       </c>
       <c r="I275" s="8">
-        <v>194</v>
+        <v>504</v>
       </c>
       <c r="J275" s="9" t="s">
         <v>20</v>
@@ -11616,7 +11562,7 @@
     </row>
     <row r="276" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A276" s="10" t="s">
-        <v>640</v>
+        <v>624</v>
       </c>
       <c r="B276" s="11" t="s">
         <v>22</v>
@@ -11634,13 +11580,13 @@
         <v>26</v>
       </c>
       <c r="G276" s="12" t="s">
-        <v>641</v>
-      </c>
-      <c r="H276" s="16" t="s">
-        <v>129</v>
+        <v>27</v>
+      </c>
+      <c r="H276" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I276" s="13">
-        <v>731</v>
+        <v>972</v>
       </c>
       <c r="J276" s="15" t="s">
         <v>43</v>
@@ -11648,7 +11594,7 @@
     </row>
     <row r="277" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A277" s="4" t="s">
-        <v>642</v>
+        <v>625</v>
       </c>
       <c r="B277" s="5" t="s">
         <v>30</v>
@@ -11672,7 +11618,7 @@
         <v>19</v>
       </c>
       <c r="I277" s="8">
-        <v>393</v>
+        <v>669</v>
       </c>
       <c r="J277" s="9" t="s">
         <v>20</v>
@@ -11680,7 +11626,7 @@
     </row>
     <row r="278" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A278" s="10" t="s">
-        <v>643</v>
+        <v>626</v>
       </c>
       <c r="B278" s="12" t="s">
         <v>37</v>
@@ -11704,7 +11650,7 @@
         <v>19</v>
       </c>
       <c r="I278" s="13">
-        <v>918</v>
+        <v>295</v>
       </c>
       <c r="J278" s="14" t="s">
         <v>28</v>
@@ -11712,7 +11658,7 @@
     </row>
     <row r="279" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A279" s="4" t="s">
-        <v>644</v>
+        <v>627</v>
       </c>
       <c r="B279" s="5" t="s">
         <v>45</v>
@@ -11736,7 +11682,7 @@
         <v>19</v>
       </c>
       <c r="I279" s="8">
-        <v>278</v>
+        <v>244</v>
       </c>
       <c r="J279" s="9" t="s">
         <v>20</v>
@@ -11744,7 +11690,7 @@
     </row>
     <row r="280" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A280" s="10" t="s">
-        <v>645</v>
+        <v>628</v>
       </c>
       <c r="B280" s="11" t="s">
         <v>52</v>
@@ -11768,7 +11714,7 @@
         <v>19</v>
       </c>
       <c r="I280" s="13">
-        <v>952</v>
+        <v>381</v>
       </c>
       <c r="J280" s="15" t="s">
         <v>43</v>
@@ -11776,7 +11722,7 @@
     </row>
     <row r="281" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A281" s="4" t="s">
-        <v>646</v>
+        <v>629</v>
       </c>
       <c r="B281" s="6" t="s">
         <v>59</v>
@@ -11800,7 +11746,7 @@
         <v>19</v>
       </c>
       <c r="I281" s="8">
-        <v>645</v>
+        <v>635</v>
       </c>
       <c r="J281" s="9" t="s">
         <v>20</v>
@@ -11808,7 +11754,7 @@
     </row>
     <row r="282" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A282" s="10" t="s">
-        <v>647</v>
+        <v>630</v>
       </c>
       <c r="B282" s="12" t="s">
         <v>66</v>
@@ -11832,7 +11778,7 @@
         <v>19</v>
       </c>
       <c r="I282" s="13">
-        <v>319</v>
+        <v>190</v>
       </c>
       <c r="J282" s="14" t="s">
         <v>28</v>
@@ -11840,7 +11786,7 @@
     </row>
     <row r="283" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A283" s="4" t="s">
-        <v>648</v>
+        <v>631</v>
       </c>
       <c r="B283" s="6" t="s">
         <v>73</v>
@@ -11864,7 +11810,7 @@
         <v>19</v>
       </c>
       <c r="I283" s="8">
-        <v>723</v>
+        <v>426</v>
       </c>
       <c r="J283" s="9" t="s">
         <v>20</v>
@@ -11872,22 +11818,22 @@
     </row>
     <row r="284" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A284" s="10" t="s">
-        <v>649</v>
+        <v>632</v>
       </c>
       <c r="B284" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C284" s="12" t="s">
-        <v>650</v>
+        <v>633</v>
       </c>
       <c r="D284" s="12" t="s">
-        <v>651</v>
+        <v>634</v>
       </c>
       <c r="E284" s="12" t="s">
         <v>83</v>
       </c>
       <c r="F284" s="12" t="s">
-        <v>652</v>
+        <v>635</v>
       </c>
       <c r="G284" s="12" t="s">
         <v>85</v>
@@ -11896,7 +11842,7 @@
         <v>19</v>
       </c>
       <c r="I284" s="13">
-        <v>457</v>
+        <v>519</v>
       </c>
       <c r="J284" s="16" t="s">
         <v>86</v>
@@ -11904,7 +11850,7 @@
     </row>
     <row r="285" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A285" s="4" t="s">
-        <v>653</v>
+        <v>636</v>
       </c>
       <c r="B285" s="5" t="s">
         <v>13</v>
@@ -11928,7 +11874,7 @@
         <v>19</v>
       </c>
       <c r="I285" s="8">
-        <v>889</v>
+        <v>191</v>
       </c>
       <c r="J285" s="9" t="s">
         <v>20</v>
@@ -11936,7 +11882,7 @@
     </row>
     <row r="286" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A286" s="10" t="s">
-        <v>654</v>
+        <v>637</v>
       </c>
       <c r="B286" s="11" t="s">
         <v>22</v>
@@ -11960,7 +11906,7 @@
         <v>19</v>
       </c>
       <c r="I286" s="13">
-        <v>366</v>
+        <v>761</v>
       </c>
       <c r="J286" s="14" t="s">
         <v>28</v>
@@ -11968,7 +11914,7 @@
     </row>
     <row r="287" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A287" s="4" t="s">
-        <v>655</v>
+        <v>638</v>
       </c>
       <c r="B287" s="5" t="s">
         <v>30</v>
@@ -11992,7 +11938,7 @@
         <v>19</v>
       </c>
       <c r="I287" s="8">
-        <v>191</v>
+        <v>319</v>
       </c>
       <c r="J287" s="9" t="s">
         <v>20</v>
@@ -12000,7 +11946,7 @@
     </row>
     <row r="288" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A288" s="10" t="s">
-        <v>656</v>
+        <v>639</v>
       </c>
       <c r="B288" s="12" t="s">
         <v>37</v>
@@ -12024,7 +11970,7 @@
         <v>19</v>
       </c>
       <c r="I288" s="13">
-        <v>415</v>
+        <v>950</v>
       </c>
       <c r="J288" s="15" t="s">
         <v>43</v>
@@ -12032,7 +11978,7 @@
     </row>
     <row r="289" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A289" s="4" t="s">
-        <v>657</v>
+        <v>640</v>
       </c>
       <c r="B289" s="5" t="s">
         <v>45</v>
@@ -12056,7 +12002,7 @@
         <v>19</v>
       </c>
       <c r="I289" s="8">
-        <v>233</v>
+        <v>907</v>
       </c>
       <c r="J289" s="9" t="s">
         <v>20</v>
@@ -12064,7 +12010,7 @@
     </row>
     <row r="290" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A290" s="10" t="s">
-        <v>658</v>
+        <v>641</v>
       </c>
       <c r="B290" s="11" t="s">
         <v>52</v>
@@ -12088,7 +12034,7 @@
         <v>19</v>
       </c>
       <c r="I290" s="13">
-        <v>912</v>
+        <v>695</v>
       </c>
       <c r="J290" s="14" t="s">
         <v>28</v>
@@ -12096,7 +12042,7 @@
     </row>
     <row r="291" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A291" s="4" t="s">
-        <v>659</v>
+        <v>642</v>
       </c>
       <c r="B291" s="6" t="s">
         <v>59</v>
@@ -12114,13 +12060,13 @@
         <v>127</v>
       </c>
       <c r="G291" s="6" t="s">
-        <v>216</v>
+        <v>128</v>
       </c>
       <c r="H291" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I291" s="8">
-        <v>607</v>
+        <v>544</v>
       </c>
       <c r="J291" s="9" t="s">
         <v>20</v>
@@ -12128,31 +12074,31 @@
     </row>
     <row r="292" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A292" s="10" t="s">
-        <v>660</v>
+        <v>643</v>
       </c>
       <c r="B292" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C292" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="D292" s="12" t="s">
         <v>131</v>
       </c>
-      <c r="D292" s="12" t="s">
+      <c r="E292" s="12" t="s">
         <v>132</v>
       </c>
-      <c r="E292" s="12" t="s">
+      <c r="F292" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="F292" s="12" t="s">
+      <c r="G292" s="11" t="s">
         <v>134</v>
       </c>
-      <c r="G292" s="11" t="s">
-        <v>135</v>
-      </c>
       <c r="H292" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I292" s="13">
-        <v>656</v>
+        <v>200</v>
       </c>
       <c r="J292" s="15" t="s">
         <v>43</v>
@@ -12160,31 +12106,31 @@
     </row>
     <row r="293" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A293" s="4" t="s">
-        <v>661</v>
+        <v>644</v>
       </c>
       <c r="B293" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C293" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D293" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D293" s="6" t="s">
+      <c r="E293" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E293" s="6" t="s">
+      <c r="F293" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="F293" s="6" t="s">
+      <c r="G293" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="G293" s="6" t="s">
-        <v>662</v>
-      </c>
-      <c r="H293" s="16" t="s">
-        <v>129</v>
+      <c r="H293" s="7" t="s">
+        <v>19</v>
       </c>
       <c r="I293" s="8">
-        <v>289</v>
+        <v>849</v>
       </c>
       <c r="J293" s="9" t="s">
         <v>20</v>
@@ -12192,31 +12138,31 @@
     </row>
     <row r="294" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A294" s="10" t="s">
-        <v>663</v>
+        <v>645</v>
       </c>
       <c r="B294" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C294" s="12" t="s">
-        <v>664</v>
+        <v>646</v>
       </c>
       <c r="D294" s="12" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E294" s="12" t="s">
-        <v>665</v>
+        <v>647</v>
       </c>
       <c r="F294" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G294" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G294" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H294" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I294" s="13">
-        <v>611</v>
+        <v>671</v>
       </c>
       <c r="J294" s="16" t="s">
         <v>86</v>
@@ -12224,31 +12170,31 @@
     </row>
     <row r="295" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A295" s="4" t="s">
-        <v>666</v>
+        <v>648</v>
       </c>
       <c r="B295" s="5" t="s">
         <v>13</v>
       </c>
       <c r="C295" s="6" t="s">
-        <v>667</v>
+        <v>649</v>
       </c>
       <c r="D295" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="E295" s="6" t="s">
-        <v>668</v>
+        <v>650</v>
       </c>
       <c r="F295" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G295" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G295" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H295" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I295" s="8">
-        <v>684</v>
+        <v>282</v>
       </c>
       <c r="J295" s="9" t="s">
         <v>20</v>
@@ -12256,31 +12202,31 @@
     </row>
     <row r="296" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A296" s="10" t="s">
-        <v>669</v>
+        <v>651</v>
       </c>
       <c r="B296" s="11" t="s">
         <v>22</v>
       </c>
       <c r="C296" s="12" t="s">
-        <v>670</v>
+        <v>652</v>
       </c>
       <c r="D296" s="12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E296" s="12" t="s">
-        <v>671</v>
+        <v>653</v>
       </c>
       <c r="F296" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G296" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G296" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H296" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I296" s="13">
-        <v>617</v>
+        <v>601</v>
       </c>
       <c r="J296" s="15" t="s">
         <v>43</v>
@@ -12288,31 +12234,31 @@
     </row>
     <row r="297" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A297" s="4" t="s">
-        <v>672</v>
+        <v>654</v>
       </c>
       <c r="B297" s="5" t="s">
         <v>30</v>
       </c>
       <c r="C297" s="6" t="s">
-        <v>673</v>
+        <v>655</v>
       </c>
       <c r="D297" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E297" s="6" t="s">
-        <v>674</v>
+        <v>656</v>
       </c>
       <c r="F297" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G297" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G297" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H297" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I297" s="8">
-        <v>257</v>
+        <v>946</v>
       </c>
       <c r="J297" s="9" t="s">
         <v>20</v>
@@ -12320,31 +12266,31 @@
     </row>
     <row r="298" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A298" s="10" t="s">
-        <v>675</v>
+        <v>657</v>
       </c>
       <c r="B298" s="12" t="s">
         <v>37</v>
       </c>
       <c r="C298" s="12" t="s">
-        <v>676</v>
+        <v>658</v>
       </c>
       <c r="D298" s="12" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="E298" s="12" t="s">
-        <v>677</v>
+        <v>659</v>
       </c>
       <c r="F298" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G298" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G298" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H298" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I298" s="13">
-        <v>377</v>
+        <v>339</v>
       </c>
       <c r="J298" s="14" t="s">
         <v>28</v>
@@ -12352,31 +12298,31 @@
     </row>
     <row r="299" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A299" s="4" t="s">
-        <v>678</v>
+        <v>660</v>
       </c>
       <c r="B299" s="5" t="s">
         <v>45</v>
       </c>
       <c r="C299" s="6" t="s">
-        <v>679</v>
+        <v>661</v>
       </c>
       <c r="D299" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="E299" s="6" t="s">
-        <v>680</v>
+        <v>662</v>
       </c>
       <c r="F299" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G299" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G299" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H299" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I299" s="8">
-        <v>704</v>
+        <v>648</v>
       </c>
       <c r="J299" s="9" t="s">
         <v>20</v>
@@ -12384,31 +12330,31 @@
     </row>
     <row r="300" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A300" s="10" t="s">
-        <v>681</v>
+        <v>663</v>
       </c>
       <c r="B300" s="11" t="s">
         <v>52</v>
       </c>
       <c r="C300" s="12" t="s">
-        <v>682</v>
+        <v>664</v>
       </c>
       <c r="D300" s="12" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="E300" s="12" t="s">
-        <v>683</v>
+        <v>665</v>
       </c>
       <c r="F300" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G300" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G300" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H300" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I300" s="13">
-        <v>870</v>
+        <v>374</v>
       </c>
       <c r="J300" s="15" t="s">
         <v>43</v>
@@ -12416,31 +12362,31 @@
     </row>
     <row r="301" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A301" s="4" t="s">
-        <v>684</v>
+        <v>666</v>
       </c>
       <c r="B301" s="6" t="s">
         <v>59</v>
       </c>
       <c r="C301" s="6" t="s">
-        <v>685</v>
+        <v>667</v>
       </c>
       <c r="D301" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="E301" s="6" t="s">
-        <v>686</v>
+        <v>668</v>
       </c>
       <c r="F301" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G301" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G301" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H301" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I301" s="8">
-        <v>681</v>
+        <v>259</v>
       </c>
       <c r="J301" s="9" t="s">
         <v>20</v>
@@ -12448,31 +12394,31 @@
     </row>
     <row r="302" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A302" s="10" t="s">
-        <v>687</v>
+        <v>669</v>
       </c>
       <c r="B302" s="12" t="s">
         <v>66</v>
       </c>
       <c r="C302" s="12" t="s">
-        <v>688</v>
+        <v>670</v>
       </c>
       <c r="D302" s="12" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="E302" s="12" t="s">
-        <v>689</v>
+        <v>671</v>
       </c>
       <c r="F302" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G302" s="11" t="s">
         <v>146</v>
       </c>
-      <c r="G302" s="11" t="s">
-        <v>147</v>
-      </c>
       <c r="H302" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I302" s="13">
-        <v>469</v>
+        <v>969</v>
       </c>
       <c r="J302" s="14" t="s">
         <v>28</v>
@@ -12480,31 +12426,31 @@
     </row>
     <row r="303" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A303" s="4" t="s">
-        <v>690</v>
+        <v>672</v>
       </c>
       <c r="B303" s="6" t="s">
         <v>73</v>
       </c>
       <c r="C303" s="6" t="s">
-        <v>691</v>
+        <v>673</v>
       </c>
       <c r="D303" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="E303" s="6" t="s">
-        <v>692</v>
+        <v>674</v>
       </c>
       <c r="F303" s="6" t="s">
+        <v>145</v>
+      </c>
+      <c r="G303" s="5" t="s">
         <v>146</v>
       </c>
-      <c r="G303" s="5" t="s">
-        <v>147</v>
-      </c>
       <c r="H303" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I303" s="8">
-        <v>618</v>
+        <v>649</v>
       </c>
       <c r="J303" s="9" t="s">
         <v>20</v>
@@ -12512,31 +12458,31 @@
     </row>
     <row r="304" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A304" s="10" t="s">
-        <v>693</v>
+        <v>675</v>
       </c>
       <c r="B304" s="12" t="s">
         <v>80</v>
       </c>
       <c r="C304" s="12" t="s">
+        <v>184</v>
+      </c>
+      <c r="D304" s="12" t="s">
         <v>185</v>
       </c>
-      <c r="D304" s="12" t="s">
+      <c r="E304" s="12" t="s">
         <v>186</v>
       </c>
-      <c r="E304" s="12" t="s">
+      <c r="F304" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="F304" s="12" t="s">
+      <c r="G304" s="12" t="s">
         <v>188</v>
       </c>
-      <c r="G304" s="12" t="s">
-        <v>189</v>
-      </c>
       <c r="H304" s="7" t="s">
         <v>19</v>
       </c>
       <c r="I304" s="13">
-        <v>338</v>
+        <v>280</v>
       </c>
       <c r="J304" s="16" t="s">
         <v>86</v>
